--- a/Unova_Path.xlsx
+++ b/Unova_Path.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F239"/>
+  <dimension ref="A1:F256"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6280,247 +6280,801 @@
         </is>
       </c>
       <c r="C226" t="inlineStr"/>
-      <c r="D226" t="inlineStr"/>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>Roggenrola</t>
+        </is>
+      </c>
       <c r="E226" t="inlineStr">
         <is>
           <t>76-78</t>
         </is>
       </c>
-      <c r="F226" t="inlineStr"/>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Nature Sanctuary</t>
+          <t>Cave of Being</t>
         </is>
       </c>
       <c r="C227" t="inlineStr"/>
-      <c r="D227" t="inlineStr"/>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>Axew</t>
+        </is>
+      </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>78-80</t>
-        </is>
-      </c>
-      <c r="F227" t="inlineStr"/>
+          <t>76-78</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Pinwheel Forest</t>
+          <t>Nature Sanctuary</t>
         </is>
       </c>
       <c r="C228" t="inlineStr"/>
-      <c r="D228" t="inlineStr"/>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>Yanma</t>
+        </is>
+      </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>80-81</t>
-        </is>
-      </c>
-      <c r="F228" t="inlineStr"/>
+          <t>78-80</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Nacrene City</t>
+          <t>Nature Sanctuary</t>
         </is>
       </c>
       <c r="C229" t="inlineStr"/>
-      <c r="D229" t="inlineStr"/>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Zorua</t>
+        </is>
+      </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>81-83</t>
-        </is>
-      </c>
-      <c r="F229" t="inlineStr"/>
+          <t>78-80</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Moor of Icirrus</t>
+          <t>Pinwheel Forest</t>
         </is>
       </c>
       <c r="C230" t="inlineStr"/>
-      <c r="D230" t="inlineStr"/>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Larvesta</t>
+        </is>
+      </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>83-85</t>
-        </is>
-      </c>
-      <c r="F230" t="inlineStr"/>
+          <t>80-81</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>33.34%</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Icirrus City</t>
+          <t>Pinwheel Forest</t>
         </is>
       </c>
       <c r="C231" t="inlineStr"/>
-      <c r="D231" t="inlineStr"/>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>Snivy</t>
+        </is>
+      </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>85-86</t>
-        </is>
-      </c>
-      <c r="F231" t="inlineStr"/>
+          <t>80-81</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>33.33%</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Striaton City</t>
+          <t>Pinwheel Forest</t>
         </is>
       </c>
       <c r="C232" t="inlineStr"/>
-      <c r="D232" t="inlineStr"/>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>Pansage</t>
+        </is>
+      </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>86-88</t>
-        </is>
-      </c>
-      <c r="F232" t="inlineStr"/>
+          <t>80-81</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>33.33%</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Dreamyard</t>
+          <t>Nacrene City</t>
         </is>
       </c>
       <c r="C233" t="inlineStr"/>
-      <c r="D233" t="inlineStr"/>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Aron</t>
+        </is>
+      </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>88-90</t>
-        </is>
-      </c>
-      <c r="F233" t="inlineStr"/>
+          <t>81-83</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>33.34%</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Wellspring Cave</t>
+          <t>Nacrene City</t>
         </is>
       </c>
       <c r="C234" t="inlineStr"/>
-      <c r="D234" t="inlineStr"/>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Tympole</t>
+        </is>
+      </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>90-91</t>
-        </is>
-      </c>
-      <c r="F234" t="inlineStr"/>
+          <t>81-83</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>33.33%</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>P2 Laboratory</t>
+          <t>Nacrene City</t>
         </is>
       </c>
       <c r="C235" t="inlineStr"/>
-      <c r="D235" t="inlineStr"/>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>Budew</t>
+        </is>
+      </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>91-93</t>
-        </is>
-      </c>
-      <c r="F235" t="inlineStr"/>
+          <t>81-83</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>33.33%</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Route 1</t>
+          <t>Moor of Icirrus</t>
         </is>
       </c>
       <c r="C236" t="inlineStr"/>
-      <c r="D236" t="inlineStr"/>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>Vullaby</t>
+        </is>
+      </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>93-95</t>
-        </is>
-      </c>
-      <c r="F236" t="inlineStr"/>
+          <t>83-85</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>33.34%</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Route 2</t>
+          <t>Moor of Icirrus</t>
         </is>
       </c>
       <c r="C237" t="inlineStr"/>
-      <c r="D237" t="inlineStr"/>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>Shelmet</t>
+        </is>
+      </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>95-96</t>
-        </is>
-      </c>
-      <c r="F237" t="inlineStr"/>
+          <t>83-85</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>33.33%</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Route 3</t>
+          <t>Moor of Icirrus</t>
         </is>
       </c>
       <c r="C238" t="inlineStr"/>
-      <c r="D238" t="inlineStr"/>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>Ducklett</t>
+        </is>
+      </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>96-98</t>
-        </is>
-      </c>
-      <c r="F238" t="inlineStr"/>
+          <t>83-85</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>33.33%</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
+        <v>49</v>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Icirrus City</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr"/>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>Lapras</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>85-86</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="n">
+        <v>49</v>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Icirrus City</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr"/>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>Tirtouga</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>85-86</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="n">
+        <v>50</v>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Striaton City</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr"/>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>Panpour</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>86-88</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="n">
+        <v>50</v>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Striaton City</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr"/>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>Pansear</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>86-88</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
+        <v>51</v>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Dreamyard</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr"/>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>Munna</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>88-90</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="n">
+        <v>51</v>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Dreamyard</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr"/>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>Rufflet</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>88-90</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="n">
+        <v>52</v>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Wellspring Cave</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr"/>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>Grimer</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>90-91</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
+        <v>52</v>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Wellspring Cave</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr"/>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>Bronzor</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>90-91</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="n">
+        <v>53</v>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>P2 Laboratory</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr"/>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>Beldum</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>91-93</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
+        <v>53</v>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>P2 Laboratory</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr"/>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>Pawniard</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>91-93</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="n">
+        <v>54</v>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Route 1</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr"/>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>Tepig</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>93-95</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="n">
+        <v>54</v>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Route 1</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr"/>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>Oshawott</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>93-95</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="n">
+        <v>55</v>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Route 2</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr"/>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>Blitzle</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>95-96</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="n">
+        <v>55</v>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Route 2</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr"/>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>Spoink</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>95-96</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="n">
+        <v>56</v>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Route 3</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr"/>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>Throh</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>96-98</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="n">
+        <v>56</v>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Route 3</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr"/>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Sawk</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>96-98</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="n">
         <v>57</v>
       </c>
-      <c r="B239" t="inlineStr">
+      <c r="B255" t="inlineStr">
         <is>
           <t>Nuvema Town</t>
         </is>
       </c>
-      <c r="C239" t="inlineStr"/>
-      <c r="D239" t="inlineStr"/>
-      <c r="E239" t="inlineStr">
+      <c r="C255" t="inlineStr"/>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>Cleffa</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
         <is>
           <t>98-100</t>
         </is>
       </c>
-      <c r="F239" t="inlineStr"/>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="n">
+        <v>57</v>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Nuvema Town</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr"/>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>Igglybuff</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>98-100</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7151,7 +7705,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Extra Challenge 1$1</t>
+          <t>Extra Challenge A$1</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -7168,7 +7722,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Extra Challenge 1$2</t>
+          <t>Extra Challenge A$2</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -7185,7 +7739,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Extra Challenge 1$3</t>
+          <t>Extra Challenge A$3</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -7202,7 +7756,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Extra Challenge 1$4</t>
+          <t>Extra Challenge A$4</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -7219,7 +7773,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Extra Challenge 1$5</t>
+          <t>Extra Challenge A$5</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -7236,7 +7790,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Extra Challenge 2$1</t>
+          <t>Extra Challenge B$1</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -7253,7 +7807,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Extra Challenge 2$2</t>
+          <t>Extra Challenge B$2</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -7270,7 +7824,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Extra Challenge 2$3</t>
+          <t>Extra Challenge B$3</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -7287,7 +7841,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Extra Challenge 2$4</t>
+          <t>Extra Challenge B$4</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -7304,7 +7858,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Extra Challenge 3$1</t>
+          <t>Extra Challenge C$1</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -7321,7 +7875,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Extra Challenge 3$2</t>
+          <t>Extra Challenge C$2</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -7338,7 +7892,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Extra Challenge 3$3</t>
+          <t>Extra Challenge C$3</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -7355,7 +7909,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Extra Challenge 3$4</t>
+          <t>Extra Challenge C$4</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -7372,7 +7926,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Extra Challenge 4$1</t>
+          <t>Extra Challenge D$1</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -7389,7 +7943,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Extra Challenge 4$2</t>
+          <t>Extra Challenge D$2</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -7406,7 +7960,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Extra Challenge 4$3</t>
+          <t>Extra Challenge D$3</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -7423,7 +7977,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Extra Challenge 4$4</t>
+          <t>Extra Challenge D$4</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -7440,7 +7994,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Extra Challenge 5$1</t>
+          <t>Extra Challenge E$1</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -7457,7 +8011,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Extra Challenge 5$2</t>
+          <t>Extra Challenge E$2</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -7474,7 +8028,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Extra Challenge 5$3</t>
+          <t>Extra Challenge E$3</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -7491,7 +8045,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Extra Challenge 5$4</t>
+          <t>Extra Challenge E$4</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -7516,7 +8070,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D168"/>
+  <dimension ref="A1:D137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7566,7 +8120,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Snivy</t>
+          <t>Servine</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -7576,183 +8130,183 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Servine</t>
+          <t>Pignite</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Grass</t>
+          <t>Fire / Fighting</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Tepig</t>
+          <t>Emboar</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Fire / Fighting</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Pignite</t>
+          <t>Dewott</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Fire / Fighting</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Emboar</t>
+          <t>Samurott</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Fire / Fighting</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Oshawott</t>
+          <t>Unfezant</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Normal / Flying</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Dewott</t>
+          <t>Swadloon</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Bug / Grass</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Samurott</t>
+          <t>Leavanny</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Bug / Grass</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Unfezant</t>
+          <t>Sunflora</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Normal / Flying</t>
+          <t>Grass</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -7764,17 +8318,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Swadloon</t>
+          <t>Herdier</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bug / Grass</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -7786,39 +8340,39 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Leavanny</t>
+          <t>Stoutland</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Bug / Grass</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sunflora</t>
+          <t>Flaaffy</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Grass</t>
+          <t>Electric</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -7830,17 +8384,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Herdier</t>
+          <t>Ampharos</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Electric</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -7852,39 +8406,39 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Stoutland</t>
+          <t>Azumarill</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Water / Fairy</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Flaaffy</t>
+          <t>Lucario</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Electric</t>
+          <t>Fighting / Steel</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -7896,39 +8450,39 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Ampharos</t>
+          <t>Simisage</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Electric</t>
+          <t>Grass</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Azumarill</t>
+          <t>Simisear</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Water / Fairy</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -7940,17 +8494,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Lucario</t>
+          <t>Simipour</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Fighting / Steel</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -7962,149 +8516,149 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Pansage</t>
+          <t>Whirlipede</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Grass</t>
+          <t>Bug / Poison</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Simisage</t>
+          <t>Scolipede</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Grass</t>
+          <t>Bug / Poison</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Pansear</t>
+          <t>Weezing</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Poison</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Simisear</t>
+          <t>Magneton</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Electric / Steel</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Panpour</t>
+          <t>Magnezone</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Electric / Steel</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Simipour</t>
+          <t>Arcanine</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Whirlipede</t>
+          <t>Magmar</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Bug / Poison</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -8116,39 +8670,39 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Scolipede</t>
+          <t>Magmortar</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Bug / Poison</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Weezing</t>
+          <t>Electabuzz</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Poison</t>
+          <t>Electric</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -8160,17 +8714,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Magneton</t>
+          <t>Electivire</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Electric / Steel</t>
+          <t>Electric</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -8182,39 +8736,39 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Magnezone</t>
+          <t>Crobat</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Electric / Steel</t>
+          <t>Poison / Flying</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Arcanine</t>
+          <t>Swoobat</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Psychic / Flying</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -8226,17 +8780,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Magmar</t>
+          <t>Gigalith</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Rock</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -8248,39 +8802,39 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Magmortar</t>
+          <t>Steelix</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Steel / Ground</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Electabuzz</t>
+          <t>Conkeldurr</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Electric</t>
+          <t>Fighting</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -8292,39 +8846,39 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Electivire</t>
+          <t>Musharna</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Electric</t>
+          <t>Psychic</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Crobat</t>
+          <t>Clefable</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Poison / Flying</t>
+          <t>Fairy</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -8336,39 +8890,39 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Grimer</t>
+          <t>Vaporeon</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Poison</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Swoobat</t>
+          <t>Jolteon</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Psychic / Flying</t>
+          <t>Electric</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8380,39 +8934,39 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Roggenrola</t>
+          <t>Flareon</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Rock</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Gigalith</t>
+          <t>Espeon</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Rock</t>
+          <t>Psychic</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8424,17 +8978,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Steelix</t>
+          <t>Umbreon</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Steel / Ground</t>
+          <t>Dark</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8446,17 +9000,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Conkeldurr</t>
+          <t>Leafeon</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Fighting</t>
+          <t>Grass</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8468,78 +9022,78 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Munna</t>
+          <t>Glaceon</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Psychic</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Musharna</t>
+          <t>Krokorok</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Psychic</t>
+          <t>Ground / Dark</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Cleffa</t>
+          <t>Krookodile</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Fairy</t>
+          <t>Ground / Dark</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Clefable</t>
+          <t>Darmanitan</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Fairy</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -8549,24 +9103,24 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Vaporeon</t>
+          <t>Cinccino</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8578,17 +9132,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Jolteon</t>
+          <t>Sandslash</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Electric</t>
+          <t>Ground</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8600,17 +9154,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Flareon</t>
+          <t>Scrafty</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Dark / Fighting</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8622,17 +9176,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Espeon</t>
+          <t>Vibrava</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Psychic</t>
+          <t>Ground / Dragon</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8644,17 +9198,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Umbreon</t>
+          <t>Flygon</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Dark</t>
+          <t>Ground / Dragon</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8666,17 +9220,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Leafeon</t>
+          <t>Cofagrigus</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Grass</t>
+          <t>Ghost</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8688,17 +9242,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Glaceon</t>
+          <t>Carracosta</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Water / Rock</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -8710,12 +9264,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Krokorok</t>
+          <t>Archen</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Ground / Dark</t>
+          <t>Rock / Flying</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -8725,19 +9279,19 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Krookodile</t>
+          <t>Archeops</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Ground / Dark</t>
+          <t>Rock / Flying</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -8754,17 +9308,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Darmanitan</t>
+          <t>Klang</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -8776,17 +9330,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Cinccino</t>
+          <t>Klinklang</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -8798,61 +9352,61 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Rufflet</t>
+          <t>Vespiquen</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Normal / Flying</t>
+          <t>Bug / Flying</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Vullaby</t>
+          <t>Zoroark</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Dark / Flying</t>
+          <t>Dark</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sandslash</t>
+          <t>Swanna</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Ground</t>
+          <t>Water / Flying</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8864,17 +9418,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Scrafty</t>
+          <t>Escavalier</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Dark / Fighting</t>
+          <t>Bug / Steel</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8886,17 +9440,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Vibrava</t>
+          <t>Accelgor</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Ground / Dragon</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8908,34 +9462,34 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Flygon</t>
+          <t>Sawsbuck</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Ground / Dragon</t>
+          <t>Normal / Grass</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Cofagrigus</t>
+          <t>Castform</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Ghost</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -8945,63 +9499,63 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Tirtouga</t>
+          <t>Probopass</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Water / Rock</t>
+          <t>Rock / Steel</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Carracosta</t>
+          <t>Aggron</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Water / Rock</t>
+          <t>Steel / Rock</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Archen</t>
+          <t>Baltoy</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Rock / Flying</t>
+          <t>Ground / Psychic</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -9018,12 +9572,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Archeops</t>
+          <t>Claydol</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Rock / Flying</t>
+          <t>Ground / Psychic</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -9040,17 +9594,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Klang</t>
+          <t>Volcarona</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Bug / Fire</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9062,61 +9616,61 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Klinklang</t>
+          <t>Galvantula</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Bug / Electric</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Budew</t>
+          <t>Ferrothorn</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Grass / Poison</t>
+          <t>Grass / Steel</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Vespiquen</t>
+          <t>Eelektross</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Bug / Flying</t>
+          <t>Electric</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9128,56 +9682,56 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Blitzle</t>
+          <t>Fraxure</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Electric</t>
+          <t>Dragon</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Zorua</t>
+          <t>Haxorus</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Dark</t>
+          <t>Dragon</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Zoroark</t>
+          <t>Zangoose</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Dark</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -9194,12 +9748,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Ducklett</t>
+          <t>Seviper</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Water / Flying</t>
+          <t>Poison</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -9216,39 +9770,39 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Swanna</t>
+          <t>Beheeyem</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Water / Flying</t>
+          <t>Psychic</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Escavalier</t>
+          <t>Lampent</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Bug / Steel</t>
+          <t>Ghost / Fire</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9260,56 +9814,56 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Shelmet</t>
+          <t>Chandelure</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Ghost / Fire</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Accelgor</t>
+          <t>Beartic</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Sawsbuck</t>
+          <t>Tornadus</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Normal / Grass</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -9319,19 +9873,19 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Castform</t>
+          <t>Thundurus</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -9348,12 +9902,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Probopass</t>
+          <t>Landorus</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Rock / Steel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -9363,19 +9917,19 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Aron</t>
+          <t>Skorupi</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Steel / Rock</t>
+          <t>Poison / Bug</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -9392,12 +9946,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Aggron</t>
+          <t>Drapion</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Steel / Rock</t>
+          <t>Poison / Dark</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -9407,19 +9961,19 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Baltoy</t>
+          <t>Numel</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Ground / Psychic</t>
+          <t>Fire / Ground</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -9436,34 +9990,34 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Claydol</t>
+          <t>Grumpig</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Ground / Psychic</t>
+          <t>Psychic</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Larvesta</t>
+          <t>Drifloon</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Bug / Fire</t>
+          <t>Ghost / Flying</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -9480,12 +10034,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Volcarona</t>
+          <t>Shuppet</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Bug / Fire</t>
+          <t>Ghost</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -9502,12 +10056,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Galvantula</t>
+          <t>Lunatone</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Bug / Electric</t>
+          <t>Rock / Psychic</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -9517,19 +10071,19 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Ferrothorn</t>
+          <t>Solrock</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Grass / Steel</t>
+          <t>Rock / Psychic</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -9539,24 +10093,24 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Eelektross</t>
+          <t>Tangrowth</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Electric</t>
+          <t>Grass</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -9568,78 +10122,78 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Axew</t>
+          <t>Mienshao</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Dragon</t>
+          <t>Fighting</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Fraxure</t>
+          <t>Gliscor</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Dragon</t>
+          <t>Ground / Flying</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Haxorus</t>
+          <t>Bisharp</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Dragon</t>
+          <t>Dark / Steel</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Zangoose</t>
+          <t>Cobalion</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Steel / Fighting</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -9656,12 +10210,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Seviper</t>
+          <t>Terrakion</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Poison</t>
+          <t>Rock / Fighting</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -9678,12 +10232,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Beheeyem</t>
+          <t>Virizion</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Psychic</t>
+          <t>Grass / Fighting</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -9693,24 +10247,24 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Lampent</t>
+          <t>Seismitoad</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Ghost / Fire</t>
+          <t>Water / Ground</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -9722,12 +10276,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Chandelure</t>
+          <t>Shuckle</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Ghost / Fire</t>
+          <t>Bug / Rock</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -9744,17 +10298,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Beartic</t>
+          <t>Mantine</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Water / Flying</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -9766,17 +10320,17 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Tornadus</t>
+          <t>Octillery</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -9788,17 +10342,17 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Thundurus</t>
+          <t>Starmie</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Water / Psychic</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -9810,12 +10364,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Landorus</t>
+          <t>Wailmer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -9825,19 +10379,19 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Skorupi</t>
+          <t>Wailord</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Poison / Bug</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -9854,193 +10408,193 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Drapion</t>
+          <t>Sealeo</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Poison / Dark</t>
+          <t>Ice / Water</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Numel</t>
+          <t>Walrein</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Fire / Ground</t>
+          <t>Ice / Water</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Spoink</t>
+          <t>Ninetales</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Psychic</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Grumpig</t>
+          <t>Weavile</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Psychic</t>
+          <t>Dark / Ice</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Drifloon</t>
+          <t>Vanillish</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Ghost / Flying</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Shuppet</t>
+          <t>Vanilluxe</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Ghost</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Lunatone</t>
+          <t>Mamoswine</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Rock / Psychic</t>
+          <t>Ice / Ground</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Solrock</t>
+          <t>Metagross</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Rock / Psychic</t>
+          <t>Steel / Psychic</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Tangrowth</t>
+          <t>Dewgong</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Grass</t>
+          <t>Water / Ice</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -10052,17 +10606,17 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Mienshao</t>
+          <t>Golurk</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Fighting</t>
+          <t>Ground / Ghost</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -10074,17 +10628,17 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Gliscor</t>
+          <t>Zweilous</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Ground / Flying</t>
+          <t>Dark / Dragon</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -10096,34 +10650,34 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Pawniard</t>
+          <t>Hydreigon</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Dark / Steel</t>
+          <t>Dark / Dragon</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Bisharp</t>
+          <t>Slakoth</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Dark / Steel</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -10140,12 +10694,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Cobalion</t>
+          <t>Vigoroth</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Steel / Fighting</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -10162,12 +10716,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Terrakion</t>
+          <t>Slaking</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Rock / Fighting</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -10184,61 +10738,61 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Virizion</t>
+          <t>Crawdaunt</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Grass / Fighting</t>
+          <t>Water / Dark</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Tympole</t>
+          <t>Jigglypuff</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Normal / Fairy</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Seismitoad</t>
+          <t>Wigglytuff</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Water / Ground</t>
+          <t>Normal / Fairy</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -10250,12 +10804,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Shuckle</t>
+          <t>Lickitung</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Bug / Rock</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -10272,12 +10826,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Mantine</t>
+          <t>Lickilicky</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Water / Flying</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -10287,24 +10841,24 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Octillery</t>
+          <t>Yanmega</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Bug / Flying</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -10316,12 +10870,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Starmie</t>
+          <t>Tropius</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Water / Psychic</t>
+          <t>Grass / Flying</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -10331,41 +10885,41 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Wailmer</t>
+          <t>Toxicroak</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Poison / Fighting</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Wailord</t>
+          <t>Larvitar</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Rock / Ground</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -10382,34 +10936,34 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Lapras</t>
+          <t>Tyranitar</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Water / Ice</t>
+          <t>Rock / Dark</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Sealeo</t>
+          <t>Reshiram</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Ice / Water</t>
+          <t>Dragon / Fire</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -10419,19 +10973,19 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Walrein</t>
+          <t>Zekrom</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Ice / Water</t>
+          <t>Dragon / Electric</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -10448,12 +11002,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Ninetales</t>
+          <t>Kyurem</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Dragon / Ice</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -10463,19 +11017,19 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Bronzor</t>
+          <t>Keldeo</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Steel / Psychic</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -10492,12 +11046,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Weavile</t>
+          <t>Meloetta</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Dark / Ice</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -10507,19 +11061,19 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Vanillish</t>
+          <t>Genesect</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Bug / Steel</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -10528,688 +11082,6 @@
         </is>
       </c>
       <c r="D137" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>Vanilluxe</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>Ice</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>Suggest: Route 1</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>Mamoswine</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>Ice / Ground</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>Suggest: Route 1</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>Beldum</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>Steel / Psychic</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>Suggest: Route 1</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>Metagross</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>Steel / Psychic</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>Suggest: Route 1</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>Dewgong</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>Water / Ice</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>Suggest: Route 1</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>Throh</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>Fighting</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>Suggest: Route 1</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>Sawk</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>Fighting</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>Suggest: Route 1</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>Golurk</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>Ground / Ghost</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>Suggest: Route 1</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>Zweilous</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>Dark / Dragon</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>Suggest: Route 1</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>Hydreigon</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>Dark / Dragon</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>Suggest: Route 1</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>Slakoth</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>Suggest: Route 1</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>Vigoroth</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>Suggest: Route 1</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>Slaking</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>Suggest: Route 1</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>Crawdaunt</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>Water / Dark</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>Suggest: Route 1</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>Igglybuff</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>Normal / Fairy</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>Suggest: Route 1</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>Jigglypuff</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>Normal / Fairy</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>Suggest: Route 1</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>Wigglytuff</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>Normal / Fairy</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>Suggest: Route 1</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>Lickitung</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>Suggest: Route 1</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>Lickilicky</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>Suggest: Route 1</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>Yanma</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>Bug / Flying</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>Suggest: Route 1</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>Yanmega</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>Bug / Flying</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>Suggest: Route 1</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>Tropius</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>Grass / Flying</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>Suggest: Route 1</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>Toxicroak</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>Poison / Fighting</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>Suggest: Route 1</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>Larvitar</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>Rock / Ground</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>Suggest: Route 1</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>Tyranitar</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>Rock / Dark</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>Suggest: Route 1</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>Reshiram</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>Dragon / Fire</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>Suggest: Route 1</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>Zekrom</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>Dragon / Electric</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>Suggest: Route 1</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>Kyurem</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>Dragon / Ice</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>Suggest: Route 1</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>Keldeo</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>Suggest: Route 1</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>Meloetta</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>Suggest: Route 1</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>Genesect</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>Bug / Steel</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>Suggest: Route 1</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr">
         <is>
           <t>No</t>
         </is>

--- a/Unova_Path.xlsx
+++ b/Unova_Path.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F256"/>
+  <dimension ref="A1:F266"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6386,7 +6386,7 @@
       <c r="C230" t="inlineStr"/>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Larvesta</t>
+          <t>Snivy</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
@@ -6396,7 +6396,7 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>33.34%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -6412,7 +6412,7 @@
       <c r="C231" t="inlineStr"/>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Snivy</t>
+          <t>Pansage</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
@@ -6422,33 +6422,33 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>33.33%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Pinwheel Forest</t>
+          <t>Nacrene City</t>
         </is>
       </c>
       <c r="C232" t="inlineStr"/>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Pansage</t>
+          <t>Tympole</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>80-81</t>
+          <t>81-83</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>33.33%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -6464,7 +6464,7 @@
       <c r="C233" t="inlineStr"/>
       <c r="D233" t="inlineStr">
         <is>
-          <t>Aron</t>
+          <t>Budew</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -6474,158 +6474,158 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>33.34%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Nacrene City</t>
+          <t>Moor of Icirrus</t>
         </is>
       </c>
       <c r="C234" t="inlineStr"/>
       <c r="D234" t="inlineStr">
         <is>
-          <t>Tympole</t>
+          <t>Shelmet</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>81-83</t>
+          <t>83-85</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>33.33%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Nacrene City</t>
+          <t>Moor of Icirrus</t>
         </is>
       </c>
       <c r="C235" t="inlineStr"/>
       <c r="D235" t="inlineStr">
         <is>
-          <t>Budew</t>
+          <t>Ducklett</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>81-83</t>
+          <t>83-85</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>33.33%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Moor of Icirrus</t>
+          <t>Icirrus City</t>
         </is>
       </c>
       <c r="C236" t="inlineStr"/>
       <c r="D236" t="inlineStr">
         <is>
-          <t>Vullaby</t>
+          <t>Lapras</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>83-85</t>
+          <t>85-86</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>33.34%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Moor of Icirrus</t>
+          <t>Icirrus City</t>
         </is>
       </c>
       <c r="C237" t="inlineStr"/>
       <c r="D237" t="inlineStr">
         <is>
-          <t>Shelmet</t>
+          <t>Tirtouga</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>83-85</t>
+          <t>85-86</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>33.33%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Moor of Icirrus</t>
+          <t>Striaton City</t>
         </is>
       </c>
       <c r="C238" t="inlineStr"/>
       <c r="D238" t="inlineStr">
         <is>
-          <t>Ducklett</t>
+          <t>Panpour</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>83-85</t>
+          <t>86-88</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>33.33%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Icirrus City</t>
+          <t>Striaton City</t>
         </is>
       </c>
       <c r="C239" t="inlineStr"/>
       <c r="D239" t="inlineStr">
         <is>
-          <t>Lapras</t>
+          <t>Pansear</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>85-86</t>
+          <t>86-88</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
@@ -6636,22 +6636,22 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Icirrus City</t>
+          <t>Dreamyard</t>
         </is>
       </c>
       <c r="C240" t="inlineStr"/>
       <c r="D240" t="inlineStr">
         <is>
-          <t>Tirtouga</t>
+          <t>Munna</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>85-86</t>
+          <t>88-90</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
@@ -6662,22 +6662,22 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Striaton City</t>
+          <t>Dreamyard</t>
         </is>
       </c>
       <c r="C241" t="inlineStr"/>
       <c r="D241" t="inlineStr">
         <is>
-          <t>Panpour</t>
+          <t>Rufflet</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>86-88</t>
+          <t>88-90</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
@@ -6688,22 +6688,22 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Striaton City</t>
+          <t>Wellspring Cave</t>
         </is>
       </c>
       <c r="C242" t="inlineStr"/>
       <c r="D242" t="inlineStr">
         <is>
-          <t>Pansear</t>
+          <t>Grimer</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>86-88</t>
+          <t>90-91</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
@@ -6714,22 +6714,22 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Dreamyard</t>
+          <t>Wellspring Cave</t>
         </is>
       </c>
       <c r="C243" t="inlineStr"/>
       <c r="D243" t="inlineStr">
         <is>
-          <t>Munna</t>
+          <t>Bronzor</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>88-90</t>
+          <t>90-91</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
@@ -6740,22 +6740,22 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Dreamyard</t>
+          <t>P2 Laboratory</t>
         </is>
       </c>
       <c r="C244" t="inlineStr"/>
       <c r="D244" t="inlineStr">
         <is>
-          <t>Rufflet</t>
+          <t>Beldum</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>88-90</t>
+          <t>91-93</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
@@ -6766,22 +6766,22 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Wellspring Cave</t>
+          <t>P2 Laboratory</t>
         </is>
       </c>
       <c r="C245" t="inlineStr"/>
       <c r="D245" t="inlineStr">
         <is>
-          <t>Grimer</t>
+          <t>Pawniard</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>90-91</t>
+          <t>91-93</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
@@ -6792,22 +6792,22 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Wellspring Cave</t>
+          <t>Route 1</t>
         </is>
       </c>
       <c r="C246" t="inlineStr"/>
       <c r="D246" t="inlineStr">
         <is>
-          <t>Bronzor</t>
+          <t>Tepig</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>90-91</t>
+          <t>93-95</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
@@ -6818,22 +6818,22 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>P2 Laboratory</t>
+          <t>Route 1</t>
         </is>
       </c>
       <c r="C247" t="inlineStr"/>
       <c r="D247" t="inlineStr">
         <is>
-          <t>Beldum</t>
+          <t>Oshawott</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>91-93</t>
+          <t>93-95</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
@@ -6844,22 +6844,22 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>P2 Laboratory</t>
+          <t>Route 2</t>
         </is>
       </c>
       <c r="C248" t="inlineStr"/>
       <c r="D248" t="inlineStr">
         <is>
-          <t>Pawniard</t>
+          <t>Blitzle</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>91-93</t>
+          <t>95-96</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
@@ -6870,22 +6870,22 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Route 1</t>
+          <t>Route 2</t>
         </is>
       </c>
       <c r="C249" t="inlineStr"/>
       <c r="D249" t="inlineStr">
         <is>
-          <t>Tepig</t>
+          <t>Spoink</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>93-95</t>
+          <t>95-96</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
@@ -6896,22 +6896,22 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Route 1</t>
+          <t>Route 3</t>
         </is>
       </c>
       <c r="C250" t="inlineStr"/>
       <c r="D250" t="inlineStr">
         <is>
-          <t>Oshawott</t>
+          <t>Throh</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>93-95</t>
+          <t>96-98</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
@@ -6922,22 +6922,22 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Route 2</t>
+          <t>Route 3</t>
         </is>
       </c>
       <c r="C251" t="inlineStr"/>
       <c r="D251" t="inlineStr">
         <is>
-          <t>Blitzle</t>
+          <t>Sawk</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>95-96</t>
+          <t>96-98</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
@@ -6948,22 +6948,22 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Route 2</t>
+          <t>Nuvema Town</t>
         </is>
       </c>
       <c r="C252" t="inlineStr"/>
       <c r="D252" t="inlineStr">
         <is>
-          <t>Spoink</t>
+          <t>Cleffa</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>95-96</t>
+          <t>98-100</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
@@ -6974,22 +6974,22 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Route 3</t>
+          <t>Nuvema Town</t>
         </is>
       </c>
       <c r="C253" t="inlineStr"/>
       <c r="D253" t="inlineStr">
         <is>
-          <t>Throh</t>
+          <t>Igglybuff</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>96-98</t>
+          <t>98-100</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
@@ -7000,79 +7000,339 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Route 3</t>
+          <t>Moor of Icirrus Depths</t>
         </is>
       </c>
       <c r="C254" t="inlineStr"/>
       <c r="D254" t="inlineStr">
         <is>
-          <t>Sawk</t>
+          <t>Cobalion</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>96-98</t>
+          <t>110</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Nuvema Town</t>
+          <t>Moor of Icirrus Depths</t>
         </is>
       </c>
       <c r="C255" t="inlineStr"/>
       <c r="D255" t="inlineStr">
         <is>
-          <t>Cleffa</t>
+          <t>Terrakion</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>98-100</t>
+          <t>110</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Nuvema Town</t>
+          <t>Moor of Icirrus Depths</t>
         </is>
       </c>
       <c r="C256" t="inlineStr"/>
       <c r="D256" t="inlineStr">
         <is>
-          <t>Igglybuff</t>
+          <t>Virizion</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>98-100</t>
+          <t>110</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>25.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="n">
+        <v>58</v>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Moor of Icirrus Depths</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr"/>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>Keldeo</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="n">
+        <v>59</v>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Liberty Garden</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr"/>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>Victini</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>33.34%</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="n">
+        <v>59</v>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Liberty Garden</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr"/>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>Meloetta</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>33.33%</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="n">
+        <v>59</v>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Liberty Garden</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr"/>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>Genesect</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>33.33%</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="n">
+        <v>60</v>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Abundant Shrine Depths</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr"/>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>Landorus</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>33.34%</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="n">
+        <v>60</v>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Abundant Shrine Depths</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr"/>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>Thundurus</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>33.33%</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="n">
+        <v>60</v>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Abundant Shrine Depths</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr"/>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>Tornadus</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>33.33%</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="n">
+        <v>61</v>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>N's Castle</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr"/>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>Kyurem</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>33.34%</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="n">
+        <v>61</v>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>N's Castle</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr"/>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>Reshiram</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>33.33%</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="n">
+        <v>61</v>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>N's Castle</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr"/>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>Zekrom</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>33.33%</t>
         </is>
       </c>
     </row>
@@ -7087,7 +7347,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C57"/>
+  <dimension ref="A1:C61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7926,136 +8186,204 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Extra Challenge D$1</t>
+          <t>Extra Challenge C$5</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Complete Challenge 35</t>
+          <t>Catch 10 Pokemon in Icirrus City</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Unlock Striaton City</t>
+          <t>Unlock Moor of Icirrus Depths</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Extra Challenge D$2</t>
+          <t>Extra Challenge D$1</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Catch 10 Pokemon in Striaton City</t>
+          <t>Complete Challenge 35</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Unlock Dreamyard</t>
+          <t>Unlock Striaton City</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Extra Challenge D$3</t>
+          <t>Extra Challenge D$2</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Catch 10 Pokemon in Dreamyard</t>
+          <t>Catch 10 Pokemon in Striaton City</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Unlock Wellspring Cave</t>
+          <t>Unlock Dreamyard</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Extra Challenge D$4</t>
+          <t>Extra Challenge D$3</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Catch 10 Pokemon in Wellspring Cave</t>
+          <t>Catch 10 Pokemon in Dreamyard</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Unlock P2 Laboratory</t>
+          <t>Unlock Wellspring Cave</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Extra Challenge E$1</t>
+          <t>Extra Challenge D$4</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Complete Challenge 35</t>
+          <t>Catch 10 Pokemon in Wellspring Cave</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Unlock Route 1</t>
+          <t>Unlock P2 Laboratory</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Extra Challenge E$2</t>
+          <t>Extra Challenge D$5</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Catch 10 Pokemon in Route 1</t>
+          <t>Catch 10 Pokemon in P2 Laboratory</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Unlock Route 2</t>
+          <t>Unlock Liberty Garden</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Extra Challenge E$3</t>
+          <t>Extra Challenge E$1</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Catch 10 Pokemon in Route 2</t>
+          <t>Complete Challenge 35</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Unlock Route 3</t>
+          <t>Unlock Route 1</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
+          <t>Extra Challenge E$2</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Catch 10 Pokemon in Route 1</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Unlock Route 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Extra Challenge E$3</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Catch 10 Pokemon in Route 2</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Unlock Route 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
           <t>Extra Challenge E$4</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t>Catch 10 Pokemon in Route 3</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>Unlock Nuvema Town</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Extra Challenge E$5</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Catch 10 Pokemon in Nuvema Town</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Unlock Abundant Shrine Depths</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Final Extra Challenge</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Complete Extra Challenge C$5, D$5, and E$5</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Unlock N's Castle</t>
         </is>
       </c>
     </row>
@@ -8070,7 +8398,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D137"/>
+  <dimension ref="A1:D127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8098,34 +8426,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Victini</t>
+          <t>Servine</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Psychic / Fire</t>
+          <t>Grass</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Servine</t>
+          <t>Pignite</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Grass</t>
+          <t>Fire / Fighting</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -8142,7 +8470,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pignite</t>
+          <t>Emboar</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -8164,12 +8492,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Emboar</t>
+          <t>Dewott</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Fire / Fighting</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -8186,7 +8514,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Dewott</t>
+          <t>Samurott</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -8208,12 +8536,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Samurott</t>
+          <t>Unfezant</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Normal / Flying</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -8230,12 +8558,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Unfezant</t>
+          <t>Swadloon</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Normal / Flying</t>
+          <t>Bug / Grass</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -8252,7 +8580,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Swadloon</t>
+          <t>Leavanny</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -8274,12 +8602,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Leavanny</t>
+          <t>Sunflora</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bug / Grass</t>
+          <t>Grass</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -8296,12 +8624,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sunflora</t>
+          <t>Herdier</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Grass</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -8318,7 +8646,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Herdier</t>
+          <t>Stoutland</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -8340,12 +8668,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Stoutland</t>
+          <t>Flaaffy</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Electric</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -8362,7 +8690,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Flaaffy</t>
+          <t>Ampharos</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -8384,12 +8712,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Ampharos</t>
+          <t>Azumarill</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Electric</t>
+          <t>Water / Fairy</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -8406,12 +8734,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Azumarill</t>
+          <t>Lucario</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Water / Fairy</t>
+          <t>Fighting / Steel</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -8428,12 +8756,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Lucario</t>
+          <t>Simisage</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Fighting / Steel</t>
+          <t>Grass</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -8450,12 +8778,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Simisage</t>
+          <t>Simisear</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Grass</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -8472,12 +8800,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Simisear</t>
+          <t>Simipour</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -8494,12 +8822,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Simipour</t>
+          <t>Whirlipede</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Bug / Poison</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -8516,7 +8844,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Whirlipede</t>
+          <t>Scolipede</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -8538,12 +8866,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Scolipede</t>
+          <t>Weezing</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Bug / Poison</t>
+          <t>Poison</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -8560,12 +8888,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Weezing</t>
+          <t>Magneton</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Poison</t>
+          <t>Electric / Steel</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -8582,7 +8910,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Magneton</t>
+          <t>Magnezone</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -8604,12 +8932,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Magnezone</t>
+          <t>Arcanine</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Electric / Steel</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -8626,7 +8954,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Arcanine</t>
+          <t>Magmar</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -8648,7 +8976,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Magmar</t>
+          <t>Magmortar</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -8670,12 +8998,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Magmortar</t>
+          <t>Electabuzz</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Electric</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -8692,7 +9020,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Electabuzz</t>
+          <t>Electivire</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -8714,12 +9042,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Electivire</t>
+          <t>Crobat</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Electric</t>
+          <t>Poison / Flying</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -8736,12 +9064,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Crobat</t>
+          <t>Swoobat</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Poison / Flying</t>
+          <t>Psychic / Flying</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -8758,12 +9086,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Swoobat</t>
+          <t>Gigalith</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Psychic / Flying</t>
+          <t>Rock</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -8780,12 +9108,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gigalith</t>
+          <t>Steelix</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Rock</t>
+          <t>Steel / Ground</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -8802,12 +9130,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Steelix</t>
+          <t>Conkeldurr</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Steel / Ground</t>
+          <t>Fighting</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -8824,12 +9152,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Conkeldurr</t>
+          <t>Musharna</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Fighting</t>
+          <t>Psychic</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -8846,12 +9174,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Musharna</t>
+          <t>Clefable</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Psychic</t>
+          <t>Fairy</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -8868,12 +9196,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Clefable</t>
+          <t>Vaporeon</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Fairy</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -8890,12 +9218,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Vaporeon</t>
+          <t>Jolteon</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Electric</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -8912,12 +9240,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Jolteon</t>
+          <t>Flareon</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Electric</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -8934,12 +9262,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Flareon</t>
+          <t>Espeon</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Psychic</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -8956,12 +9284,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Espeon</t>
+          <t>Umbreon</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Psychic</t>
+          <t>Dark</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -8978,12 +9306,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Umbreon</t>
+          <t>Leafeon</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Dark</t>
+          <t>Grass</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -9000,12 +9328,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Leafeon</t>
+          <t>Glaceon</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Grass</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -9022,12 +9350,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Glaceon</t>
+          <t>Krokorok</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Ground / Dark</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -9044,7 +9372,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Krokorok</t>
+          <t>Krookodile</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -9066,66 +9394,66 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Krookodile</t>
+          <t>Darmanitan</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Ground / Dark</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Suggest: Route 1</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Darmanitan</t>
+          <t>Cinccino</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Cinccino</t>
+          <t>Vullaby</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Dark / Flying</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Suggest: Route 1</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9528,7 +9856,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Aggron</t>
+          <t>Aron</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -9538,41 +9866,41 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Suggest: Route 1</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Baltoy</t>
+          <t>Aggron</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Ground / Psychic</t>
+          <t>Steel / Rock</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Claydol</t>
+          <t>Baltoy</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -9594,78 +9922,78 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Volcarona</t>
+          <t>Claydol</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Bug / Fire</t>
+          <t>Ground / Psychic</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Suggest: Route 1</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Galvantula</t>
+          <t>Larvesta</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Bug / Electric</t>
+          <t>Bug / Fire</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Suggest: Route 1</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Ferrothorn</t>
+          <t>Volcarona</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Grass / Steel</t>
+          <t>Bug / Fire</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Suggest: Route 1</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Eelektross</t>
+          <t>Galvantula</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Electric</t>
+          <t>Bug / Electric</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -9682,12 +10010,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Fraxure</t>
+          <t>Ferrothorn</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Dragon</t>
+          <t>Grass / Steel</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -9704,12 +10032,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Haxorus</t>
+          <t>Eelektross</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Dragon</t>
+          <t>Electric</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -9726,100 +10054,100 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Zangoose</t>
+          <t>Fraxure</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Dragon</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Seviper</t>
+          <t>Haxorus</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Poison</t>
+          <t>Dragon</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Beheeyem</t>
+          <t>Zangoose</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Psychic</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Suggest: Route 1</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Lampent</t>
+          <t>Seviper</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Ghost / Fire</t>
+          <t>Poison</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Suggest: Route 1</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Chandelure</t>
+          <t>Beheeyem</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Ghost / Fire</t>
+          <t>Psychic</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -9836,12 +10164,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Beartic</t>
+          <t>Lampent</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Ghost / Fire</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -9858,56 +10186,56 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Tornadus</t>
+          <t>Chandelure</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Ghost / Fire</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Thundurus</t>
+          <t>Beartic</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Landorus</t>
+          <t>Skorupi</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Poison / Bug</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -9924,12 +10252,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Skorupi</t>
+          <t>Drapion</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Poison / Bug</t>
+          <t>Poison / Dark</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -9946,12 +10274,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Drapion</t>
+          <t>Numel</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Poison / Dark</t>
+          <t>Fire / Ground</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -9968,56 +10296,56 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Numel</t>
+          <t>Grumpig</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Fire / Ground</t>
+          <t>Psychic</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Grumpig</t>
+          <t>Drifloon</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Psychic</t>
+          <t>Ghost / Flying</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Suggest: Route 1</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Drifloon</t>
+          <t>Shuppet</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Ghost / Flying</t>
+          <t>Ghost</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -10034,12 +10362,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Shuppet</t>
+          <t>Lunatone</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Ghost</t>
+          <t>Rock / Psychic</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -10056,7 +10384,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Lunatone</t>
+          <t>Solrock</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -10078,34 +10406,34 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Solrock</t>
+          <t>Tangrowth</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Rock / Psychic</t>
+          <t>Grass</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Tangrowth</t>
+          <t>Mienshao</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Grass</t>
+          <t>Fighting</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -10122,12 +10450,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Mienshao</t>
+          <t>Gliscor</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Fighting</t>
+          <t>Ground / Flying</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -10144,12 +10472,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Gliscor</t>
+          <t>Bisharp</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Ground / Flying</t>
+          <t>Dark / Steel</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -10166,12 +10494,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Bisharp</t>
+          <t>Seismitoad</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Dark / Steel</t>
+          <t>Water / Ground</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -10188,12 +10516,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Cobalion</t>
+          <t>Shuckle</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Steel / Fighting</t>
+          <t>Bug / Rock</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -10210,56 +10538,56 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Terrakion</t>
+          <t>Mantine</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Rock / Fighting</t>
+          <t>Water / Flying</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Virizion</t>
+          <t>Octillery</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Grass / Fighting</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Seismitoad</t>
+          <t>Starmie</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Water / Ground</t>
+          <t>Water / Psychic</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -10276,12 +10604,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Shuckle</t>
+          <t>Wailmer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Bug / Rock</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -10298,34 +10626,34 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Mantine</t>
+          <t>Wailord</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Water / Flying</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Suggest: Route 1</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Octillery</t>
+          <t>Sealeo</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Ice / Water</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -10342,12 +10670,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Starmie</t>
+          <t>Walrein</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Water / Psychic</t>
+          <t>Ice / Water</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -10364,56 +10692,56 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Wailmer</t>
+          <t>Ninetales</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Wailord</t>
+          <t>Weavile</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Dark / Ice</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Sealeo</t>
+          <t>Vanillish</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Ice / Water</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -10430,12 +10758,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Walrein</t>
+          <t>Vanilluxe</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Ice / Water</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -10452,12 +10780,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Ninetales</t>
+          <t>Mamoswine</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice / Ground</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -10474,12 +10802,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Weavile</t>
+          <t>Metagross</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Dark / Ice</t>
+          <t>Steel / Psychic</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -10496,12 +10824,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Vanillish</t>
+          <t>Dewgong</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Water / Ice</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -10518,12 +10846,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Vanilluxe</t>
+          <t>Golurk</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Ground / Ghost</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -10540,12 +10868,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Mamoswine</t>
+          <t>Zweilous</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Ice / Ground</t>
+          <t>Dark / Dragon</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -10562,12 +10890,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Metagross</t>
+          <t>Hydreigon</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Steel / Psychic</t>
+          <t>Dark / Dragon</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -10584,78 +10912,78 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Dewgong</t>
+          <t>Slakoth</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Water / Ice</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Suggest: Route 1</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Golurk</t>
+          <t>Vigoroth</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Ground / Ghost</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Suggest: Route 1</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Zweilous</t>
+          <t>Slaking</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Dark / Dragon</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Suggest: Route 1</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Hydreigon</t>
+          <t>Crawdaunt</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Dark / Dragon</t>
+          <t>Water / Dark</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -10672,51 +11000,51 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Slakoth</t>
+          <t>Jigglypuff</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal / Fairy</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Vigoroth</t>
+          <t>Wigglytuff</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal / Fairy</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Slaking</t>
+          <t>Lickitung</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10738,34 +11066,34 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Crawdaunt</t>
+          <t>Lickilicky</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Water / Dark</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Suggest: Route 1</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Jigglypuff</t>
+          <t>Yanmega</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Normal / Fairy</t>
+          <t>Bug / Flying</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -10782,56 +11110,56 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Wigglytuff</t>
+          <t>Tropius</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Normal / Fairy</t>
+          <t>Grass / Flying</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Suggest: Route 1</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Lickitung</t>
+          <t>Toxicroak</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Poison / Fighting</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Lickilicky</t>
+          <t>Larvitar</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Rock / Ground</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -10848,12 +11176,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Yanmega</t>
+          <t>Tyranitar</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Bug / Flying</t>
+          <t>Rock / Dark</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -10864,226 +11192,6 @@
       <c r="D127" t="inlineStr">
         <is>
           <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>Tropius</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>Grass / Flying</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>Suggest: Route 1</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>Toxicroak</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>Poison / Fighting</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>Larvitar</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>Rock / Ground</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>Suggest: Route 1</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>Tyranitar</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>Rock / Dark</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>Reshiram</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>Dragon / Fire</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>Suggest: Route 1</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>Zekrom</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>Dragon / Electric</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>Suggest: Route 1</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>Kyurem</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>Dragon / Ice</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>Suggest: Route 1</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>Keldeo</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>Suggest: Route 1</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>Meloetta</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>Suggest: Route 1</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>Genesect</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>Bug / Steel</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>Suggest: Route 1</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>No</t>
         </is>
       </c>
     </row>

--- a/Unova_Path.xlsx
+++ b/Unova_Path.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F266"/>
+  <dimension ref="A1:F263"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -909,7 +909,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>6-8</t>
+          <t>6-7</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>6-8</t>
+          <t>6-7</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>6-8</t>
+          <t>6-7</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -987,7 +987,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>6-8</t>
+          <t>6-7</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>6-8</t>
+          <t>6-7</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>6-8</t>
+          <t>6-7</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>8-9</t>
+          <t>7-9</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>8-9</t>
+          <t>7-9</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>8-9</t>
+          <t>7-9</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>8-9</t>
+          <t>7-9</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>8-9</t>
+          <t>7-9</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>8-9</t>
+          <t>7-9</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1398,7 +1398,7 @@
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Delcatty</t>
+          <t>Whimsicott</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>16.64999999999999%</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Whimsicott</t>
+          <t>Lilligant</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>16.67%</t>
         </is>
       </c>
     </row>
@@ -1450,7 +1450,7 @@
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Lilligant</t>
+          <t>Rattata</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>16.67%</t>
         </is>
       </c>
     </row>
@@ -1476,7 +1476,7 @@
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Rattata</t>
+          <t>Cottonee</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>16.67%</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Cottonee</t>
+          <t>Petilil</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1512,7 +1512,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>16.67%</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Petilil</t>
+          <t>Pidove</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1538,95 +1538,95 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>16.67%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Castelia City</t>
+          <t>Castelia Park</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Skitty</t>
+          <t>Delcatty</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>11-13</t>
+          <t>13-14</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Castelia City</t>
+          <t>Castelia Park</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Buneary</t>
+          <t>Skitty</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>11-13</t>
+          <t>13-14</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Castelia City</t>
+          <t>Castelia Park</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Pidove</t>
+          <t>Buneary</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>11-13</t>
+          <t>13-14</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Castelia City</t>
+          <t>Castelia Park</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
@@ -1637,18 +1637,18 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>11-13</t>
+          <t>13-14</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>13-15</t>
+          <t>14-16</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -1674,7 +1674,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>13-15</t>
+          <t>14-16</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -1700,7 +1700,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>13-15</t>
+          <t>14-16</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -1726,7 +1726,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>15-17</t>
+          <t>16-18</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -1752,7 +1752,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>15-17</t>
+          <t>16-18</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -1778,7 +1778,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>15-17</t>
+          <t>16-18</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -1804,7 +1804,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>15-17</t>
+          <t>16-18</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -1830,7 +1830,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>17-18</t>
+          <t>18-20</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -1856,7 +1856,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>17-18</t>
+          <t>18-20</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -1882,7 +1882,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>17-18</t>
+          <t>18-20</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -1908,7 +1908,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>17-18</t>
+          <t>18-20</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -1934,7 +1934,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -1949,7 +1949,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>18-20</t>
+          <t>20-21</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -1960,7 +1960,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>18-20</t>
+          <t>20-21</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -1986,7 +1986,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>18-20</t>
+          <t>20-21</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2012,7 +2012,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>18-20</t>
+          <t>20-21</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2038,7 +2038,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>18-20</t>
+          <t>20-21</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2064,7 +2064,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>18-20</t>
+          <t>20-21</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2090,7 +2090,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>18-20</t>
+          <t>20-21</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2116,7 +2116,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>20-22</t>
+          <t>21-23</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2142,7 +2142,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>20-22</t>
+          <t>21-23</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2168,7 +2168,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>20-22</t>
+          <t>21-23</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2194,7 +2194,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
@@ -2209,7 +2209,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>22-24</t>
+          <t>23-25</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2220,7 +2220,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>22-24</t>
+          <t>23-25</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2246,7 +2246,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>22-24</t>
+          <t>23-25</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2272,7 +2272,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>24-25</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2298,7 +2298,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>24-25</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2324,7 +2324,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
@@ -2339,7 +2339,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>24-25</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -2350,7 +2350,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>24-25</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -2376,7 +2376,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>24-25</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -2402,7 +2402,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>24-25</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -2428,7 +2428,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>25-27</t>
+          <t>26-28</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -2454,7 +2454,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
@@ -2469,7 +2469,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>25-27</t>
+          <t>26-28</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -2480,7 +2480,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>25-27</t>
+          <t>26-28</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -2506,7 +2506,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>25-27</t>
+          <t>26-28</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -2532,7 +2532,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
@@ -2547,7 +2547,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>25-27</t>
+          <t>26-28</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -2558,7 +2558,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>25-27</t>
+          <t>26-28</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -2584,7 +2584,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>27-29</t>
+          <t>28-30</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -2610,7 +2610,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
@@ -2625,7 +2625,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>27-29</t>
+          <t>28-30</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -2636,7 +2636,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
@@ -2651,7 +2651,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>27-29</t>
+          <t>28-30</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -2662,7 +2662,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>27-29</t>
+          <t>28-30</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -2688,7 +2688,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>27-29</t>
+          <t>28-30</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -2714,7 +2714,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>29-31</t>
+          <t>30-32</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -2740,7 +2740,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>29-31</t>
+          <t>30-32</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -2766,7 +2766,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
@@ -2781,7 +2781,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>29-31</t>
+          <t>30-32</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -2792,7 +2792,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>29-31</t>
+          <t>30-32</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -2818,7 +2818,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>31-33</t>
+          <t>32-33</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -2844,7 +2844,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>31-33</t>
+          <t>32-33</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -2870,7 +2870,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>31-33</t>
+          <t>32-33</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -2896,7 +2896,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>31-33</t>
+          <t>32-33</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -2922,7 +2922,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>31-33</t>
+          <t>32-33</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -2948,7 +2948,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>33-34</t>
+          <t>33-35</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -2974,7 +2974,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>33-34</t>
+          <t>33-35</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3000,7 +3000,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
@@ -3015,7 +3015,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>33-34</t>
+          <t>33-35</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3026,7 +3026,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>34-36</t>
+          <t>35-37</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3052,7 +3052,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
@@ -3067,7 +3067,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>34-36</t>
+          <t>35-37</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3078,7 +3078,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
@@ -3093,7 +3093,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>34-36</t>
+          <t>35-37</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -3104,7 +3104,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>34-36</t>
+          <t>35-37</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -3130,7 +3130,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
@@ -3145,7 +3145,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>36-38</t>
+          <t>37-39</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -3156,7 +3156,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
@@ -3171,7 +3171,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>36-38</t>
+          <t>37-39</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -3182,7 +3182,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>36-38</t>
+          <t>37-39</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -3208,7 +3208,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
@@ -3223,7 +3223,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>36-38</t>
+          <t>37-39</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -3234,7 +3234,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
@@ -3249,7 +3249,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>36-38</t>
+          <t>37-39</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -3260,7 +3260,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>36-38</t>
+          <t>37-39</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -3286,7 +3286,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
@@ -3301,7 +3301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>36-38</t>
+          <t>37-39</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -3312,7 +3312,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
@@ -3327,7 +3327,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>36-38</t>
+          <t>37-39</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -3338,7 +3338,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>38-40</t>
+          <t>39-40</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -3364,7 +3364,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>38-40</t>
+          <t>39-40</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -3390,7 +3390,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
@@ -3405,7 +3405,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>38-40</t>
+          <t>39-40</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -3416,7 +3416,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
@@ -3431,7 +3431,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>38-40</t>
+          <t>39-40</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -3442,7 +3442,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>38-40</t>
+          <t>39-40</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -3468,7 +3468,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>38-40</t>
+          <t>39-40</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -3494,7 +3494,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
@@ -3509,7 +3509,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>38-40</t>
+          <t>39-40</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -3520,7 +3520,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>38-40</t>
+          <t>39-40</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -3546,7 +3546,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>40-41</t>
+          <t>40-42</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -3572,7 +3572,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
@@ -3587,7 +3587,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>40-41</t>
+          <t>40-42</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -3598,7 +3598,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
@@ -3613,7 +3613,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>40-41</t>
+          <t>40-42</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -3624,7 +3624,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>40-41</t>
+          <t>40-42</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -3650,7 +3650,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
@@ -3665,7 +3665,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>40-41</t>
+          <t>40-42</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -3676,7 +3676,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>41-43</t>
+          <t>42-44</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -3702,7 +3702,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>41-43</t>
+          <t>42-44</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -3728,7 +3728,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>41-43</t>
+          <t>42-44</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -3754,7 +3754,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
@@ -3769,7 +3769,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>41-43</t>
+          <t>42-44</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -3780,7 +3780,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
@@ -3795,7 +3795,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>41-43</t>
+          <t>42-44</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -3806,7 +3806,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>43-45</t>
+          <t>44-45</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -3832,7 +3832,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
@@ -3847,7 +3847,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>43-45</t>
+          <t>44-45</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -3858,7 +3858,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>43-45</t>
+          <t>44-45</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -3884,7 +3884,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>43-45</t>
+          <t>44-45</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -3910,7 +3910,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>43-45</t>
+          <t>44-45</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -3936,7 +3936,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
@@ -4014,7 +4014,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
@@ -4040,7 +4040,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
@@ -4066,7 +4066,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
@@ -4092,7 +4092,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
@@ -4118,7 +4118,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
@@ -4144,7 +4144,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
@@ -4170,7 +4170,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
@@ -4211,7 +4211,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>49-50</t>
+          <t>49-51</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -4222,7 +4222,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
@@ -4237,7 +4237,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>49-50</t>
+          <t>49-51</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -4248,7 +4248,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
@@ -4263,7 +4263,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>49-50</t>
+          <t>49-51</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -4274,7 +4274,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
@@ -4289,7 +4289,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>49-50</t>
+          <t>49-51</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -4300,7 +4300,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
@@ -4315,7 +4315,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>49-50</t>
+          <t>49-51</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -4326,7 +4326,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
@@ -4341,7 +4341,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>50-52</t>
+          <t>51-52</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -4352,7 +4352,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B152" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>50-52</t>
+          <t>51-52</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -4378,7 +4378,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
@@ -4393,7 +4393,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>50-52</t>
+          <t>51-52</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -4404,7 +4404,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
@@ -4419,7 +4419,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>50-52</t>
+          <t>51-52</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -4430,7 +4430,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
@@ -4445,7 +4445,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>50-52</t>
+          <t>51-52</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -4456,7 +4456,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
@@ -4482,7 +4482,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
@@ -4508,7 +4508,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
@@ -4534,7 +4534,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B159" t="inlineStr">
         <is>
@@ -4560,7 +4560,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
@@ -4586,7 +4586,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
@@ -4612,7 +4612,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
@@ -4638,7 +4638,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
@@ -4690,7 +4690,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
@@ -4742,7 +4742,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B167" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>56-57</t>
+          <t>56-58</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -4768,7 +4768,7 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>56-57</t>
+          <t>56-58</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -4794,7 +4794,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>56-57</t>
+          <t>56-58</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -4820,7 +4820,7 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
@@ -4835,7 +4835,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>56-57</t>
+          <t>56-58</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -4846,7 +4846,7 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B171" t="inlineStr">
         <is>
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>56-57</t>
+          <t>56-58</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -4872,7 +4872,7 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B172" t="inlineStr">
         <is>
@@ -4887,7 +4887,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>57-59</t>
+          <t>58-59</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -4898,7 +4898,7 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>57-59</t>
+          <t>58-59</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -4924,7 +4924,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>57-59</t>
+          <t>58-59</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -4950,7 +4950,7 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
@@ -4965,7 +4965,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>57-59</t>
+          <t>58-59</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -4976,7 +4976,7 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B176" t="inlineStr">
         <is>
@@ -4991,7 +4991,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>57-59</t>
+          <t>58-59</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -5002,7 +5002,7 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
@@ -5017,7 +5017,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>57-59</t>
+          <t>58-59</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -5028,7 +5028,7 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B178" t="inlineStr">
         <is>
@@ -5043,7 +5043,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>57-59</t>
+          <t>58-59</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -5054,7 +5054,7 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
@@ -5080,7 +5080,7 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B180" t="inlineStr">
         <is>
@@ -5106,7 +5106,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B181" t="inlineStr">
         <is>
@@ -5132,7 +5132,7 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B182" t="inlineStr">
         <is>
@@ -5158,7 +5158,7 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B183" t="inlineStr">
         <is>
@@ -5184,7 +5184,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B184" t="inlineStr">
         <is>
@@ -5210,7 +5210,7 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B185" t="inlineStr">
         <is>
@@ -5236,7 +5236,7 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
@@ -5262,7 +5262,7 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B187" t="inlineStr">
         <is>
@@ -5288,7 +5288,7 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B188" t="inlineStr">
         <is>
@@ -5314,7 +5314,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B189" t="inlineStr">
         <is>
@@ -5336,7 +5336,7 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
@@ -5356,13 +5356,13 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B191" t="inlineStr">
         <is>
@@ -5382,13 +5382,13 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
@@ -5408,13 +5408,13 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B193" t="inlineStr">
         <is>
@@ -5434,39 +5434,39 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Route 8</t>
+          <t>Dragonspiral Tower</t>
         </is>
       </c>
       <c r="C194" t="inlineStr"/>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Barboach</t>
+          <t>Golett</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>65-66</t>
+          <t>66-68</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B195" t="inlineStr">
         <is>
@@ -5476,7 +5476,7 @@
       <c r="C195" t="inlineStr"/>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Golett</t>
+          <t>Druddigon</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -5492,7 +5492,7 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B196" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
       <c r="C196" t="inlineStr"/>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Druddigon</t>
+          <t>Mienfoo</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -5518,7 +5518,7 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B197" t="inlineStr">
         <is>
@@ -5528,7 +5528,7 @@
       <c r="C197" t="inlineStr"/>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Mienfoo</t>
+          <t>Golbat</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -5544,22 +5544,22 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Dragonspiral Tower</t>
+          <t>Twist Mountain</t>
         </is>
       </c>
       <c r="C198" t="inlineStr"/>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Golbat</t>
+          <t>Boldore</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>66-68</t>
+          <t>68-70</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -5570,7 +5570,7 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B199" t="inlineStr">
         <is>
@@ -5580,7 +5580,7 @@
       <c r="C199" t="inlineStr"/>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Boldore</t>
+          <t>Gurdurr</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -5596,7 +5596,7 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B200" t="inlineStr">
         <is>
@@ -5606,7 +5606,7 @@
       <c r="C200" t="inlineStr"/>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Gurdurr</t>
+          <t>Cryogonal</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -5622,7 +5622,7 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B201" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
       <c r="C201" t="inlineStr"/>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Cryogonal</t>
+          <t>Woobat</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -5648,33 +5648,33 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Twist Mountain</t>
+          <t>Giant Chasm</t>
         </is>
       </c>
       <c r="C202" t="inlineStr"/>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Woobat</t>
+          <t>Delibird</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>68-70</t>
+          <t>70-71</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>16.64999999999999%</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B203" t="inlineStr">
         <is>
@@ -5684,7 +5684,7 @@
       <c r="C203" t="inlineStr"/>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Delibird</t>
+          <t>Swinub</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -5694,13 +5694,13 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>16.67%</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B204" t="inlineStr">
         <is>
@@ -5710,7 +5710,7 @@
       <c r="C204" t="inlineStr"/>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Swinub</t>
+          <t>Piloswine</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -5720,13 +5720,13 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>16.67%</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B205" t="inlineStr">
         <is>
@@ -5736,7 +5736,7 @@
       <c r="C205" t="inlineStr"/>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Piloswine</t>
+          <t>Ditto</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -5746,13 +5746,13 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>16.67%</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B206" t="inlineStr">
         <is>
@@ -5762,7 +5762,7 @@
       <c r="C206" t="inlineStr"/>
       <c r="D206" t="inlineStr">
         <is>
-          <t>Ditto</t>
+          <t>Clefairy</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -5772,13 +5772,13 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>16.67%</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B207" t="inlineStr">
         <is>
@@ -5788,7 +5788,7 @@
       <c r="C207" t="inlineStr"/>
       <c r="D207" t="inlineStr">
         <is>
-          <t>Clefairy</t>
+          <t>Metang</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -5798,91 +5798,91 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>16.67%</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Giant Chasm</t>
+          <t>Underground Ruins</t>
         </is>
       </c>
       <c r="C208" t="inlineStr"/>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Metang</t>
+          <t>Boldore</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>70-71</t>
+          <t>71-73</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>16.64999999999999%</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Giant Chasm</t>
+          <t>Underground Ruins</t>
         </is>
       </c>
       <c r="C209" t="inlineStr"/>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Piloswine</t>
+          <t>Nosepass</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>70-71</t>
+          <t>71-73</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>16.67%</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Giant Chasm</t>
+          <t>Underground Ruins</t>
         </is>
       </c>
       <c r="C210" t="inlineStr"/>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Ditto</t>
+          <t>Lairon</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>70-71</t>
+          <t>71-73</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>16.67%</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B211" t="inlineStr">
         <is>
@@ -5892,7 +5892,7 @@
       <c r="C211" t="inlineStr"/>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Boldore</t>
+          <t>Woobat</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -5902,13 +5902,13 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>16.64999999999999%</t>
+          <t>16.67%</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B212" t="inlineStr">
         <is>
@@ -5918,7 +5918,7 @@
       <c r="C212" t="inlineStr"/>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Nosepass</t>
+          <t>Durant</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -5934,7 +5934,7 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B213" t="inlineStr">
         <is>
@@ -5944,7 +5944,7 @@
       <c r="C213" t="inlineStr"/>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Lairon</t>
+          <t>Onix</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -5960,85 +5960,85 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Underground Ruins</t>
+          <t>Route 15</t>
         </is>
       </c>
       <c r="C214" t="inlineStr"/>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Woobat</t>
+          <t>Gligar</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>71-73</t>
+          <t>73-75</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>16.67%</t>
+          <t>20.0%</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Underground Ruins</t>
+          <t>Route 15</t>
         </is>
       </c>
       <c r="C215" t="inlineStr"/>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Durant</t>
+          <t>Pupitar</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>71-73</t>
+          <t>73-75</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>16.67%</t>
+          <t>20.0%</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Underground Ruins</t>
+          <t>Route 15</t>
         </is>
       </c>
       <c r="C216" t="inlineStr"/>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Onix</t>
+          <t>Scraggy</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>71-73</t>
+          <t>73-75</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>16.67%</t>
+          <t>20.0%</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B217" t="inlineStr">
         <is>
@@ -6048,7 +6048,7 @@
       <c r="C217" t="inlineStr"/>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Gligar</t>
+          <t>Foongus</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -6064,7 +6064,7 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B218" t="inlineStr">
         <is>
@@ -6074,7 +6074,7 @@
       <c r="C218" t="inlineStr"/>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Pupitar</t>
+          <t>Koffing</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
@@ -6090,11 +6090,11 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Route 15</t>
+          <t>Route 18</t>
         </is>
       </c>
       <c r="C219" t="inlineStr"/>
@@ -6105,70 +6105,70 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>73-75</t>
+          <t>75-76</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Route 15</t>
+          <t>Route 18</t>
         </is>
       </c>
       <c r="C220" t="inlineStr"/>
       <c r="D220" t="inlineStr">
         <is>
-          <t>Foongus</t>
+          <t>Crustle</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>73-75</t>
+          <t>75-76</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Route 15</t>
+          <t>Route 18</t>
         </is>
       </c>
       <c r="C221" t="inlineStr"/>
       <c r="D221" t="inlineStr">
         <is>
-          <t>Koffing</t>
+          <t>Carnivine</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>73-75</t>
+          <t>75-76</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B222" t="inlineStr">
         <is>
@@ -6178,7 +6178,7 @@
       <c r="C222" t="inlineStr"/>
       <c r="D222" t="inlineStr">
         <is>
-          <t>Scraggy</t>
+          <t>Drifblim</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
@@ -6194,100 +6194,100 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Route 18</t>
+          <t>Cave of Being</t>
         </is>
       </c>
       <c r="C223" t="inlineStr"/>
       <c r="D223" t="inlineStr">
         <is>
-          <t>Crustle</t>
+          <t>Roggenrola</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>75-76</t>
+          <t>76-78</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Route 18</t>
+          <t>Cave of Being</t>
         </is>
       </c>
       <c r="C224" t="inlineStr"/>
       <c r="D224" t="inlineStr">
         <is>
-          <t>Carnivine</t>
+          <t>Axew</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>75-76</t>
+          <t>76-78</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Route 18</t>
+          <t>Nature Sanctuary</t>
         </is>
       </c>
       <c r="C225" t="inlineStr"/>
       <c r="D225" t="inlineStr">
         <is>
-          <t>Drifblim</t>
+          <t>Yanma</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>75-76</t>
+          <t>78-80</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Cave of Being</t>
+          <t>Nature Sanctuary</t>
         </is>
       </c>
       <c r="C226" t="inlineStr"/>
       <c r="D226" t="inlineStr">
         <is>
-          <t>Roggenrola</t>
+          <t>Zorua</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>76-78</t>
+          <t>78-80</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
@@ -6298,22 +6298,22 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Cave of Being</t>
+          <t>Pinwheel Forest</t>
         </is>
       </c>
       <c r="C227" t="inlineStr"/>
       <c r="D227" t="inlineStr">
         <is>
-          <t>Axew</t>
+          <t>Snivy</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>76-78</t>
+          <t>80-81</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
@@ -6324,22 +6324,22 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Nature Sanctuary</t>
+          <t>Pinwheel Forest</t>
         </is>
       </c>
       <c r="C228" t="inlineStr"/>
       <c r="D228" t="inlineStr">
         <is>
-          <t>Yanma</t>
+          <t>Pansage</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>78-80</t>
+          <t>80-81</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
@@ -6350,22 +6350,22 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Nature Sanctuary</t>
+          <t>Nacrene City</t>
         </is>
       </c>
       <c r="C229" t="inlineStr"/>
       <c r="D229" t="inlineStr">
         <is>
-          <t>Zorua</t>
+          <t>Tympole</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>78-80</t>
+          <t>81-83</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -6376,22 +6376,22 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Pinwheel Forest</t>
+          <t>Nacrene City</t>
         </is>
       </c>
       <c r="C230" t="inlineStr"/>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Snivy</t>
+          <t>Budew</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>80-81</t>
+          <t>81-83</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
@@ -6402,22 +6402,22 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Pinwheel Forest</t>
+          <t>Moor of Icirrus</t>
         </is>
       </c>
       <c r="C231" t="inlineStr"/>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Pansage</t>
+          <t>Shelmet</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>80-81</t>
+          <t>83-85</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
@@ -6428,22 +6428,22 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Nacrene City</t>
+          <t>Moor of Icirrus</t>
         </is>
       </c>
       <c r="C232" t="inlineStr"/>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Tympole</t>
+          <t>Ducklett</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>81-83</t>
+          <t>83-85</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
@@ -6454,22 +6454,22 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Nacrene City</t>
+          <t>Icirrus City</t>
         </is>
       </c>
       <c r="C233" t="inlineStr"/>
       <c r="D233" t="inlineStr">
         <is>
-          <t>Budew</t>
+          <t>Lapras</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>81-83</t>
+          <t>85-86</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
@@ -6480,22 +6480,22 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Moor of Icirrus</t>
+          <t>Icirrus City</t>
         </is>
       </c>
       <c r="C234" t="inlineStr"/>
       <c r="D234" t="inlineStr">
         <is>
-          <t>Shelmet</t>
+          <t>Tirtouga</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>83-85</t>
+          <t>85-86</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
@@ -6506,22 +6506,22 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Moor of Icirrus</t>
+          <t>Striaton City</t>
         </is>
       </c>
       <c r="C235" t="inlineStr"/>
       <c r="D235" t="inlineStr">
         <is>
-          <t>Ducklett</t>
+          <t>Panpour</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>83-85</t>
+          <t>86-88</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
@@ -6532,22 +6532,22 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Icirrus City</t>
+          <t>Striaton City</t>
         </is>
       </c>
       <c r="C236" t="inlineStr"/>
       <c r="D236" t="inlineStr">
         <is>
-          <t>Lapras</t>
+          <t>Pansear</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>85-86</t>
+          <t>86-88</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
@@ -6558,22 +6558,22 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Icirrus City</t>
+          <t>Dreamyard</t>
         </is>
       </c>
       <c r="C237" t="inlineStr"/>
       <c r="D237" t="inlineStr">
         <is>
-          <t>Tirtouga</t>
+          <t>Munna</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>85-86</t>
+          <t>88-90</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
@@ -6584,22 +6584,22 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Striaton City</t>
+          <t>Dreamyard</t>
         </is>
       </c>
       <c r="C238" t="inlineStr"/>
       <c r="D238" t="inlineStr">
         <is>
-          <t>Panpour</t>
+          <t>Rufflet</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>86-88</t>
+          <t>88-90</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
@@ -6610,22 +6610,22 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Striaton City</t>
+          <t>Wellspring Cave</t>
         </is>
       </c>
       <c r="C239" t="inlineStr"/>
       <c r="D239" t="inlineStr">
         <is>
-          <t>Pansear</t>
+          <t>Grimer</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>86-88</t>
+          <t>90-91</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
@@ -6636,22 +6636,22 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Dreamyard</t>
+          <t>Wellspring Cave</t>
         </is>
       </c>
       <c r="C240" t="inlineStr"/>
       <c r="D240" t="inlineStr">
         <is>
-          <t>Munna</t>
+          <t>Bronzor</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>88-90</t>
+          <t>90-91</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
@@ -6662,22 +6662,22 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Dreamyard</t>
+          <t>P2 Laboratory</t>
         </is>
       </c>
       <c r="C241" t="inlineStr"/>
       <c r="D241" t="inlineStr">
         <is>
-          <t>Rufflet</t>
+          <t>Beldum</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>88-90</t>
+          <t>91-93</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
@@ -6688,22 +6688,22 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Wellspring Cave</t>
+          <t>P2 Laboratory</t>
         </is>
       </c>
       <c r="C242" t="inlineStr"/>
       <c r="D242" t="inlineStr">
         <is>
-          <t>Grimer</t>
+          <t>Pawniard</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>90-91</t>
+          <t>91-93</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
@@ -6714,22 +6714,22 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Wellspring Cave</t>
+          <t>Route 1</t>
         </is>
       </c>
       <c r="C243" t="inlineStr"/>
       <c r="D243" t="inlineStr">
         <is>
-          <t>Bronzor</t>
+          <t>Tepig</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>90-91</t>
+          <t>93-95</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
@@ -6740,22 +6740,22 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>P2 Laboratory</t>
+          <t>Route 1</t>
         </is>
       </c>
       <c r="C244" t="inlineStr"/>
       <c r="D244" t="inlineStr">
         <is>
-          <t>Beldum</t>
+          <t>Oshawott</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>91-93</t>
+          <t>93-95</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
@@ -6766,22 +6766,22 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>P2 Laboratory</t>
+          <t>Route 2</t>
         </is>
       </c>
       <c r="C245" t="inlineStr"/>
       <c r="D245" t="inlineStr">
         <is>
-          <t>Pawniard</t>
+          <t>Blitzle</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>91-93</t>
+          <t>95-96</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
@@ -6792,22 +6792,22 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Route 1</t>
+          <t>Route 2</t>
         </is>
       </c>
       <c r="C246" t="inlineStr"/>
       <c r="D246" t="inlineStr">
         <is>
-          <t>Tepig</t>
+          <t>Spoink</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>93-95</t>
+          <t>95-96</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
@@ -6818,22 +6818,22 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Route 1</t>
+          <t>Route 3</t>
         </is>
       </c>
       <c r="C247" t="inlineStr"/>
       <c r="D247" t="inlineStr">
         <is>
-          <t>Oshawott</t>
+          <t>Throh</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>93-95</t>
+          <t>96-98</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
@@ -6844,22 +6844,22 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Route 2</t>
+          <t>Route 3</t>
         </is>
       </c>
       <c r="C248" t="inlineStr"/>
       <c r="D248" t="inlineStr">
         <is>
-          <t>Blitzle</t>
+          <t>Sawk</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>95-96</t>
+          <t>96-98</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
@@ -6870,22 +6870,22 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Route 2</t>
+          <t>Nuvema Town</t>
         </is>
       </c>
       <c r="C249" t="inlineStr"/>
       <c r="D249" t="inlineStr">
         <is>
-          <t>Spoink</t>
+          <t>Cleffa</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>95-96</t>
+          <t>98-100</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
@@ -6896,22 +6896,22 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Route 3</t>
+          <t>Nuvema Town</t>
         </is>
       </c>
       <c r="C250" t="inlineStr"/>
       <c r="D250" t="inlineStr">
         <is>
-          <t>Throh</t>
+          <t>Igglybuff</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>96-98</t>
+          <t>98-100</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
@@ -6922,85 +6922,85 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Route 3</t>
+          <t>Moor of Icirrus Depths</t>
         </is>
       </c>
       <c r="C251" t="inlineStr"/>
       <c r="D251" t="inlineStr">
         <is>
-          <t>Sawk</t>
+          <t>Cobalion</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>96-98</t>
+          <t>110</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Nuvema Town</t>
+          <t>Moor of Icirrus Depths</t>
         </is>
       </c>
       <c r="C252" t="inlineStr"/>
       <c r="D252" t="inlineStr">
         <is>
-          <t>Cleffa</t>
+          <t>Terrakion</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>98-100</t>
+          <t>110</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Nuvema Town</t>
+          <t>Moor of Icirrus Depths</t>
         </is>
       </c>
       <c r="C253" t="inlineStr"/>
       <c r="D253" t="inlineStr">
         <is>
-          <t>Igglybuff</t>
+          <t>Virizion</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>98-100</t>
+          <t>110</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B254" t="inlineStr">
         <is>
@@ -7010,7 +7010,7 @@
       <c r="C254" t="inlineStr"/>
       <c r="D254" t="inlineStr">
         <is>
-          <t>Cobalion</t>
+          <t>Keldeo</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -7026,17 +7026,17 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Moor of Icirrus Depths</t>
+          <t>Liberty Garden</t>
         </is>
       </c>
       <c r="C255" t="inlineStr"/>
       <c r="D255" t="inlineStr">
         <is>
-          <t>Terrakion</t>
+          <t>Victini</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -7046,23 +7046,23 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>33.34%</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Moor of Icirrus Depths</t>
+          <t>Liberty Garden</t>
         </is>
       </c>
       <c r="C256" t="inlineStr"/>
       <c r="D256" t="inlineStr">
         <is>
-          <t>Virizion</t>
+          <t>Meloetta</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -7072,23 +7072,23 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>33.33%</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Moor of Icirrus Depths</t>
+          <t>Liberty Garden</t>
         </is>
       </c>
       <c r="C257" t="inlineStr"/>
       <c r="D257" t="inlineStr">
         <is>
-          <t>Keldeo</t>
+          <t>Genesect</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
@@ -7098,23 +7098,23 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>33.33%</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Liberty Garden</t>
+          <t>Abundant Shrine Depths</t>
         </is>
       </c>
       <c r="C258" t="inlineStr"/>
       <c r="D258" t="inlineStr">
         <is>
-          <t>Victini</t>
+          <t>Landorus</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
@@ -7130,17 +7130,17 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Liberty Garden</t>
+          <t>Abundant Shrine Depths</t>
         </is>
       </c>
       <c r="C259" t="inlineStr"/>
       <c r="D259" t="inlineStr">
         <is>
-          <t>Meloetta</t>
+          <t>Thundurus</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
@@ -7156,17 +7156,17 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Liberty Garden</t>
+          <t>Abundant Shrine Depths</t>
         </is>
       </c>
       <c r="C260" t="inlineStr"/>
       <c r="D260" t="inlineStr">
         <is>
-          <t>Genesect</t>
+          <t>Tornadus</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
@@ -7182,22 +7182,22 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Abundant Shrine Depths</t>
+          <t>N's Castle</t>
         </is>
       </c>
       <c r="C261" t="inlineStr"/>
       <c r="D261" t="inlineStr">
         <is>
-          <t>Landorus</t>
+          <t>Kyurem</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>120</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
@@ -7208,22 +7208,22 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Abundant Shrine Depths</t>
+          <t>N's Castle</t>
         </is>
       </c>
       <c r="C262" t="inlineStr"/>
       <c r="D262" t="inlineStr">
         <is>
-          <t>Thundurus</t>
+          <t>Reshiram</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>120</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
@@ -7234,103 +7234,25 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Abundant Shrine Depths</t>
+          <t>N's Castle</t>
         </is>
       </c>
       <c r="C263" t="inlineStr"/>
       <c r="D263" t="inlineStr">
         <is>
-          <t>Tornadus</t>
+          <t>Zekrom</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>120</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
-        <is>
-          <t>33.33%</t>
-        </is>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" t="n">
-        <v>61</v>
-      </c>
-      <c r="B264" t="inlineStr">
-        <is>
-          <t>N's Castle</t>
-        </is>
-      </c>
-      <c r="C264" t="inlineStr"/>
-      <c r="D264" t="inlineStr">
-        <is>
-          <t>Kyurem</t>
-        </is>
-      </c>
-      <c r="E264" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="F264" t="inlineStr">
-        <is>
-          <t>33.34%</t>
-        </is>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" t="n">
-        <v>61</v>
-      </c>
-      <c r="B265" t="inlineStr">
-        <is>
-          <t>N's Castle</t>
-        </is>
-      </c>
-      <c r="C265" t="inlineStr"/>
-      <c r="D265" t="inlineStr">
-        <is>
-          <t>Reshiram</t>
-        </is>
-      </c>
-      <c r="E265" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="F265" t="inlineStr">
-        <is>
-          <t>33.33%</t>
-        </is>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" t="n">
-        <v>61</v>
-      </c>
-      <c r="B266" t="inlineStr">
-        <is>
-          <t>N's Castle</t>
-        </is>
-      </c>
-      <c r="C266" t="inlineStr"/>
-      <c r="D266" t="inlineStr">
-        <is>
-          <t>Zekrom</t>
-        </is>
-      </c>
-      <c r="E266" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="F266" t="inlineStr">
         <is>
           <t>33.33%</t>
         </is>
@@ -7347,7 +7269,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C61"/>
+  <dimension ref="A1:C62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7482,7 +7404,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Unlock Castelia Sewers</t>
+          <t>Unlock Castelia Park</t>
         </is>
       </c>
     </row>
@@ -7494,12 +7416,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Defeat Trainer in Castelia Sewers</t>
+          <t>Defeat Trainer in Castelia Park</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Unlock Relic Passage</t>
+          <t>Unlock Castelia Sewers</t>
         </is>
       </c>
     </row>
@@ -7511,12 +7433,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Defeat Trainer in Relic Passage</t>
+          <t>Defeat Trainer in Castelia Sewers</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Unlock Route 4</t>
+          <t>Unlock Relic Passage</t>
         </is>
       </c>
     </row>
@@ -7528,12 +7450,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Defeat Trainer in Route 4</t>
+          <t>Defeat Trainer in Relic Passage</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Unlock Desert Resort</t>
+          <t>Unlock Route 4</t>
         </is>
       </c>
     </row>
@@ -7545,12 +7467,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Defeat Trainer in Desert Resort</t>
+          <t>Defeat Trainer in Route 4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Unlock Relic Castle</t>
+          <t>Unlock Desert Resort</t>
         </is>
       </c>
     </row>
@@ -7562,12 +7484,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Defeat Trainer in Relic Castle</t>
+          <t>Defeat Trainer in Desert Resort</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Unlock Nimbasa City</t>
+          <t>Unlock Relic Castle</t>
         </is>
       </c>
     </row>
@@ -7579,12 +7501,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Gym Leader Elesa</t>
+          <t>Defeat Trainer in Relic Castle</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Unlock Lostal Forest</t>
+          <t>Unlock Nimbasa City</t>
         </is>
       </c>
     </row>
@@ -7596,12 +7518,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Defeat Trainer in Lostal Forest</t>
+          <t>Gym Leader Elesa</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Unlock Route 16</t>
+          <t>Unlock Lostal Forest</t>
         </is>
       </c>
     </row>
@@ -7613,12 +7535,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Defeat Trainer in Route 16</t>
+          <t>Defeat Trainer in Lostal Forest</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Unlock Route 6</t>
+          <t>Unlock Route 16</t>
         </is>
       </c>
     </row>
@@ -7630,12 +7552,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Defeat Trainer in Route 6</t>
+          <t>Defeat Trainer in Route 16</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Unlock Chargestone Cave</t>
+          <t>Unlock Route 6</t>
         </is>
       </c>
     </row>
@@ -7647,12 +7569,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Defeat Trainer in Chargestone Cave</t>
+          <t>Defeat Trainer in Route 6</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Unlock Route 7</t>
+          <t>Unlock Chargestone Cave</t>
         </is>
       </c>
     </row>
@@ -7664,12 +7586,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Defeat Trainer in Route 7</t>
+          <t>Defeat Trainer in Chargestone Cave</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Unlock Celestial Tower</t>
+          <t>Unlock Route 7</t>
         </is>
       </c>
     </row>
@@ -7681,12 +7603,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Gym Leader Skyla</t>
+          <t>Defeat Trainer in Route 7</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Unlock Reversal Mountain</t>
+          <t>Unlock Celestial Tower</t>
         </is>
       </c>
     </row>
@@ -7698,12 +7620,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Defeat Trainer in Reversal Mountain</t>
+          <t>Gym Leader Skyla</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Unlock Strange House</t>
+          <t>Unlock Reversal Mountain</t>
         </is>
       </c>
     </row>
@@ -7715,12 +7637,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Defeat Trainer in Strange House</t>
+          <t>Defeat Trainer in Reversal Mountain</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Unlock Undella Bay</t>
+          <t>Unlock Strange House</t>
         </is>
       </c>
     </row>
@@ -7732,12 +7654,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Gym Leader Drayden</t>
+          <t>Defeat Trainer in Strange House</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Unlock Route 13</t>
+          <t>Unlock Undella Bay</t>
         </is>
       </c>
     </row>
@@ -7749,12 +7671,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Defeat Trainer in Route 13</t>
+          <t>Gym Leader Drayden</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Unlock Route 14</t>
+          <t>Unlock Route 13</t>
         </is>
       </c>
     </row>
@@ -7766,12 +7688,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Defeat Trainer in Route 14</t>
+          <t>Defeat Trainer in Route 13</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Unlock Abundant Shrine</t>
+          <t>Unlock Route 14</t>
         </is>
       </c>
     </row>
@@ -7783,12 +7705,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Defeat Trainer in Abundant Shrine</t>
+          <t>Defeat Trainer in Route 14</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Unlock Village Bridge</t>
+          <t>Unlock Abundant Shrine</t>
         </is>
       </c>
     </row>
@@ -7800,12 +7722,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Defeat Trainer in Village Bridge</t>
+          <t>Defeat Trainer in Abundant Shrine</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Unlock Route 12</t>
+          <t>Unlock Village Bridge</t>
         </is>
       </c>
     </row>
@@ -7817,12 +7739,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Defeat Trainer in Route 12</t>
+          <t>Defeat Trainer in Village Bridge</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Unlock Route 9</t>
+          <t>Unlock Route 12</t>
         </is>
       </c>
     </row>
@@ -7834,12 +7756,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Defeat Trainer in Route 9</t>
+          <t>Defeat Trainer in Route 12</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Unlock Route 10</t>
+          <t>Unlock Route 9</t>
         </is>
       </c>
     </row>
@@ -7851,12 +7773,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Defeat Trainer in Route 10</t>
+          <t>Defeat Trainer in Route 9</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Unlock Driftveil Drawbridge</t>
+          <t>Unlock Route 10</t>
         </is>
       </c>
     </row>
@@ -7868,12 +7790,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Gym Leader Clay</t>
+          <t>Defeat Trainer in Route 10</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Unlock Seaside Cave</t>
+          <t>Unlock Driftveil Drawbridge</t>
         </is>
       </c>
     </row>
@@ -7885,12 +7807,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Defeat Trainer in Seaside Cave</t>
+          <t>Gym Leader Clay</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Unlock Route 21</t>
+          <t>Unlock Seaside Cave</t>
         </is>
       </c>
     </row>
@@ -7902,12 +7824,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Defeat Trainer in Route 21</t>
+          <t>Defeat Trainer in Seaside Cave</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Unlock Humilau Sea</t>
+          <t>Unlock Route 21</t>
         </is>
       </c>
     </row>
@@ -7919,12 +7841,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Gym Leader Marlon</t>
+          <t>Defeat Trainer in Route 21</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Unlock Route 23</t>
+          <t>Unlock Humilau Sea</t>
         </is>
       </c>
     </row>
@@ -7936,12 +7858,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Defeat Trainer in Route 23</t>
+          <t>Gym Leader Marlon</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Unlock Victory Road</t>
+          <t>Unlock Route 23</t>
         </is>
       </c>
     </row>
@@ -7953,435 +7875,452 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Pokemon League Champion</t>
+          <t>Defeat Trainer in Route 23</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Unlock Pokemon League</t>
+          <t>Unlock Victory Road</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Extra Challenge A$1</t>
+          <t>Challenge 36</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Complete Challenge 13</t>
+          <t>Pokemon League Champion</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Unlock Route 8</t>
+          <t>Unlock Pokemon League</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Extra Challenge A$2</t>
+          <t>Extra Challenge A$1</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Catch 10 Pokemon in Route 8</t>
+          <t>Complete Challenge 13</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Unlock Dragonspiral Tower</t>
+          <t>Unlock Route 8</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Extra Challenge A$3</t>
+          <t>Extra Challenge A$2</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Catch 10 Pokemon in Dragonspiral Tower</t>
+          <t>Catch 10 Pokemon in Route 8</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Unlock Twist Mountain</t>
+          <t>Unlock Dragonspiral Tower</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Extra Challenge A$4</t>
+          <t>Extra Challenge A$3</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Catch 10 Pokemon in Twist Mountain</t>
+          <t>Catch 10 Pokemon in Dragonspiral Tower</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Unlock Giant Chasm</t>
+          <t>Unlock Twist Mountain</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Extra Challenge A$5</t>
+          <t>Extra Challenge A$4</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Catch 10 Pokemon in Giant Chasm</t>
+          <t>Catch 10 Pokemon in Twist Mountain</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Unlock Underground Ruins</t>
+          <t>Unlock Giant Chasm</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Extra Challenge B$1</t>
+          <t>Extra Challenge A$5</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Complete Challenge 20</t>
+          <t>Catch 10 Pokemon in Giant Chasm</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Unlock Route 15</t>
+          <t>Unlock Underground Ruins</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Extra Challenge B$2</t>
+          <t>Extra Challenge B$1</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Catch 10 Pokemon in Route 15</t>
+          <t>Complete Challenge 20</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Unlock Route 18</t>
+          <t>Unlock Route 15</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Extra Challenge B$3</t>
+          <t>Extra Challenge B$2</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Catch 10 Pokemon in Route 18</t>
+          <t>Catch 10 Pokemon in Route 15</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Unlock Cave of Being</t>
+          <t>Unlock Route 18</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Extra Challenge B$4</t>
+          <t>Extra Challenge B$3</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Catch 10 Pokemon in Cave of Being</t>
+          <t>Catch 10 Pokemon in Route 18</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Unlock Nature Sanctuary</t>
+          <t>Unlock Cave of Being</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Extra Challenge C$1</t>
+          <t>Extra Challenge B$4</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Complete Challenge 35</t>
+          <t>Catch 10 Pokemon in Cave of Being</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Unlock Pinwheel Forest</t>
+          <t>Unlock Nature Sanctuary</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Extra Challenge C$2</t>
+          <t>Extra Challenge C$1</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Catch 10 Pokemon in Pinwheel Forest</t>
+          <t>Complete Challenge 36</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Unlock Nacrene City</t>
+          <t>Unlock Pinwheel Forest</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Extra Challenge C$3</t>
+          <t>Extra Challenge C$2</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Catch 10 Pokemon in Nacrene City</t>
+          <t>Catch 10 Pokemon in Pinwheel Forest</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Unlock Moor of Icirrus</t>
+          <t>Unlock Nacrene City</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Extra Challenge C$4</t>
+          <t>Extra Challenge C$3</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Catch 10 Pokemon in Moor of Icirrus</t>
+          <t>Catch 10 Pokemon in Nacrene City</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Unlock Icirrus City</t>
+          <t>Unlock Moor of Icirrus</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Extra Challenge C$5</t>
+          <t>Extra Challenge C$4</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Catch 10 Pokemon in Icirrus City</t>
+          <t>Catch 10 Pokemon in Moor of Icirrus</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Unlock Moor of Icirrus Depths</t>
+          <t>Unlock Icirrus City</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Extra Challenge D$1</t>
+          <t>Extra Challenge C$5</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Complete Challenge 35</t>
+          <t>Catch 10 Pokemon in Icirrus City</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Unlock Striaton City</t>
+          <t>Unlock Moor of Icirrus Depths</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Extra Challenge D$2</t>
+          <t>Extra Challenge D$1</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Catch 10 Pokemon in Striaton City</t>
+          <t>Complete Challenge 36</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Unlock Dreamyard</t>
+          <t>Unlock Striaton City</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Extra Challenge D$3</t>
+          <t>Extra Challenge D$2</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Catch 10 Pokemon in Dreamyard</t>
+          <t>Catch 10 Pokemon in Striaton City</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Unlock Wellspring Cave</t>
+          <t>Unlock Dreamyard</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Extra Challenge D$4</t>
+          <t>Extra Challenge D$3</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Catch 10 Pokemon in Wellspring Cave</t>
+          <t>Catch 10 Pokemon in Dreamyard</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Unlock P2 Laboratory</t>
+          <t>Unlock Wellspring Cave</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Extra Challenge D$5</t>
+          <t>Extra Challenge D$4</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Catch 10 Pokemon in P2 Laboratory</t>
+          <t>Catch 10 Pokemon in Wellspring Cave</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Unlock Liberty Garden</t>
+          <t>Unlock P2 Laboratory</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Extra Challenge E$1</t>
+          <t>Extra Challenge D$5</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Complete Challenge 35</t>
+          <t>Catch 10 Pokemon in P2 Laboratory</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Unlock Route 1</t>
+          <t>Unlock Liberty Garden</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Extra Challenge E$2</t>
+          <t>Extra Challenge E$1</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Catch 10 Pokemon in Route 1</t>
+          <t>Complete Challenge 36</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Unlock Route 2</t>
+          <t>Unlock Route 1</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Extra Challenge E$3</t>
+          <t>Extra Challenge E$2</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Catch 10 Pokemon in Route 2</t>
+          <t>Catch 10 Pokemon in Route 1</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Unlock Route 3</t>
+          <t>Unlock Route 2</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Extra Challenge E$4</t>
+          <t>Extra Challenge E$3</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Catch 10 Pokemon in Route 3</t>
+          <t>Catch 10 Pokemon in Route 2</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Unlock Nuvema Town</t>
+          <t>Unlock Route 3</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Extra Challenge E$5</t>
+          <t>Extra Challenge E$4</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Catch 10 Pokemon in Nuvema Town</t>
+          <t>Catch 10 Pokemon in Route 3</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Unlock Abundant Shrine Depths</t>
+          <t>Unlock Nuvema Town</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
+          <t>Extra Challenge E$5</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Catch 10 Pokemon in Nuvema Town</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Unlock Abundant Shrine Depths</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
           <t>Final Extra Challenge</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B62" t="inlineStr">
         <is>
           <t>Complete Extra Challenge C$5, D$5, and E$5</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C62" t="inlineStr">
         <is>
           <t>Unlock N's Castle</t>
         </is>

--- a/Unova_Path.xlsx
+++ b/Unova_Path.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F263"/>
+  <dimension ref="A1:F283"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>33.34%</t>
+          <t>16.64999999999999%</t>
         </is>
       </c>
     </row>
@@ -2162,7 +2162,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>33.33%</t>
+          <t>16.67%</t>
         </is>
       </c>
     </row>
@@ -2188,163 +2188,163 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>33.33%</t>
+          <t>16.67%</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Nimbasa City</t>
+          <t>Relic Castle</t>
         </is>
       </c>
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Pachirisu</t>
+          <t>Archen</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>23-25</t>
+          <t>21-23</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>33.34%</t>
+          <t>16.67%</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Nimbasa City</t>
+          <t>Relic Castle</t>
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Plusle</t>
+          <t>Baltoy</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>23-25</t>
+          <t>21-23</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>33.33%</t>
+          <t>16.67%</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Nimbasa City</t>
+          <t>Relic Castle</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Minun</t>
+          <t>Larvesta</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>23-25</t>
+          <t>21-23</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>33.33%</t>
+          <t>16.67%</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Lostal Forest</t>
+          <t>Nimbasa City</t>
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Heracross</t>
+          <t>Pachirisu</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>25-26</t>
+          <t>23-25</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>16.64999999999999%</t>
+          <t>33.34%</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Lostal Forest</t>
+          <t>Nimbasa City</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Pinsir</t>
+          <t>Plusle</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>25-26</t>
+          <t>23-25</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>16.67%</t>
+          <t>33.33%</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Lostal Forest</t>
+          <t>Nimbasa City</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Gothita</t>
+          <t>Minun</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>25-26</t>
+          <t>23-25</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>16.67%</t>
+          <t>33.33%</t>
         </is>
       </c>
     </row>
@@ -2360,7 +2360,7 @@
       <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Minccino</t>
+          <t>Heracross</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -2370,7 +2370,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>16.67%</t>
+          <t>14.259999999999998%</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Trubbish</t>
+          <t>Pinsir</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -2396,7 +2396,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>16.67%</t>
+          <t>14.29%</t>
         </is>
       </c>
     </row>
@@ -2412,7 +2412,7 @@
       <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Solosis</t>
+          <t>Gothita</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -2422,111 +2422,111 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>16.67%</t>
+          <t>14.29%</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Route 16</t>
+          <t>Lostal Forest</t>
         </is>
       </c>
       <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Gothitelle</t>
+          <t>Minccino</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>26-28</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>16.64999999999999%</t>
+          <t>14.29%</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Route 16</t>
+          <t>Lostal Forest</t>
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Reuniclus</t>
+          <t>Trubbish</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>26-28</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>16.67%</t>
+          <t>14.29%</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Route 16</t>
+          <t>Lostal Forest</t>
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Trubbish</t>
+          <t>Solosis</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>26-28</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>16.67%</t>
+          <t>14.29%</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Route 16</t>
+          <t>Lostal Forest</t>
         </is>
       </c>
       <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Foongus</t>
+          <t>Slakoth</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>26-28</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>16.67%</t>
+          <t>14.29%</t>
         </is>
       </c>
     </row>
@@ -2542,7 +2542,7 @@
       <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Emolga</t>
+          <t>Gothitelle</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -2552,7 +2552,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>16.67%</t>
+          <t>16.64999999999999%</t>
         </is>
       </c>
     </row>
@@ -2568,7 +2568,7 @@
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Joltik</t>
+          <t>Reuniclus</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -2584,105 +2584,105 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Route 6</t>
+          <t>Route 16</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Deerling</t>
+          <t>Trubbish</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>28-30</t>
+          <t>26-28</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>16.67%</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Route 6</t>
+          <t>Route 16</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Karrablast</t>
+          <t>Foongus</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>28-30</t>
+          <t>26-28</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>16.67%</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Route 6</t>
+          <t>Route 16</t>
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Trubbish</t>
+          <t>Emolga</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>28-30</t>
+          <t>26-28</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>16.67%</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Route 6</t>
+          <t>Route 16</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Foongus</t>
+          <t>Joltik</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>28-30</t>
+          <t>26-28</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>16.67%</t>
         </is>
       </c>
     </row>
@@ -2698,7 +2698,7 @@
       <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Vanillite</t>
+          <t>Deerling</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -2708,158 +2708,158 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>16.64999999999999%</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Chargestone Cave</t>
+          <t>Route 6</t>
         </is>
       </c>
       <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Joltik</t>
+          <t>Karrablast</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>30-32</t>
+          <t>28-30</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>16.67%</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Chargestone Cave</t>
+          <t>Route 6</t>
         </is>
       </c>
       <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Klink</t>
+          <t>Trubbish</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>30-32</t>
+          <t>28-30</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>16.67%</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Chargestone Cave</t>
+          <t>Route 6</t>
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Ferroseed</t>
+          <t>Foongus</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>30-32</t>
+          <t>28-30</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>16.67%</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Chargestone Cave</t>
+          <t>Route 6</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Tynamo</t>
+          <t>Vanillite</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>30-32</t>
+          <t>28-30</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>16.67%</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Route 7</t>
+          <t>Route 6</t>
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Deerling</t>
+          <t>Castform</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>32-33</t>
+          <t>28-30</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>16.67%</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Route 7</t>
+          <t>Chargestone Cave</t>
         </is>
       </c>
       <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Watchog</t>
+          <t>Joltik</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>32-33</t>
+          <t>30-32</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -2870,22 +2870,22 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Route 7</t>
+          <t>Chargestone Cave</t>
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Foongus</t>
+          <t>Klink</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>32-33</t>
+          <t>30-32</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -2896,22 +2896,22 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Route 7</t>
+          <t>Chargestone Cave</t>
         </is>
       </c>
       <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Cubchoo</t>
+          <t>Ferroseed</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>32-33</t>
+          <t>30-32</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -2922,22 +2922,22 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Route 7</t>
+          <t>Chargestone Cave</t>
         </is>
       </c>
       <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Zebstrika</t>
+          <t>Tynamo</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>32-33</t>
+          <t>30-32</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -2948,1244 +2948,1244 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Celestial Tower</t>
+          <t>Chargestone Cave</t>
         </is>
       </c>
       <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Litwick</t>
+          <t>Aron</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>33-35</t>
+          <t>30-32</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>33.34%</t>
+          <t>20.0%</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Celestial Tower</t>
+          <t>Route 7</t>
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Elgyem</t>
+          <t>Deerling</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>33-35</t>
+          <t>32-33</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>33.33%</t>
+          <t>14.259999999999998%</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Celestial Tower</t>
+          <t>Route 7</t>
         </is>
       </c>
       <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Golbat</t>
+          <t>Watchog</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>33-35</t>
+          <t>32-33</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>33.33%</t>
+          <t>14.29%</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Reversal Mountain</t>
+          <t>Route 7</t>
         </is>
       </c>
       <c r="C101" t="inlineStr"/>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Skarmory</t>
+          <t>Foongus</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>35-37</t>
+          <t>32-33</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>14.29%</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Reversal Mountain</t>
+          <t>Route 7</t>
         </is>
       </c>
       <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Camerupt</t>
+          <t>Cubchoo</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>35-37</t>
+          <t>32-33</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>14.29%</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Reversal Mountain</t>
+          <t>Route 7</t>
         </is>
       </c>
       <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Excadrill</t>
+          <t>Zebstrika</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>35-37</t>
+          <t>32-33</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>14.29%</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Reversal Mountain</t>
+          <t>Route 7</t>
         </is>
       </c>
       <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Lopunny</t>
+          <t>Zangoose</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>35-37</t>
+          <t>32-33</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>14.29%</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Strange House</t>
+          <t>Route 7</t>
         </is>
       </c>
       <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Litwick</t>
+          <t>Seviper</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>37-39</t>
+          <t>32-33</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>14.29%</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Strange House</t>
+          <t>Celestial Tower</t>
         </is>
       </c>
       <c r="C106" t="inlineStr"/>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Raticate</t>
+          <t>Litwick</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>37-39</t>
+          <t>33-35</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>33.34%</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Strange House</t>
+          <t>Celestial Tower</t>
         </is>
       </c>
       <c r="C107" t="inlineStr"/>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Golbat</t>
+          <t>Elgyem</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>37-39</t>
+          <t>33-35</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>33.33%</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Strange House</t>
+          <t>Celestial Tower</t>
         </is>
       </c>
       <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Banette</t>
+          <t>Golbat</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>37-39</t>
+          <t>33-35</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>33.33%</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Strange House</t>
+          <t>Reversal Mountain</t>
         </is>
       </c>
       <c r="C109" t="inlineStr"/>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Gothita</t>
+          <t>Skarmory</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>37-39</t>
+          <t>35-37</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>16.64999999999999%</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Strange House</t>
+          <t>Reversal Mountain</t>
         </is>
       </c>
       <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Solosis</t>
+          <t>Camerupt</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>37-39</t>
+          <t>35-37</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>16.67%</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Strange House</t>
+          <t>Reversal Mountain</t>
         </is>
       </c>
       <c r="C111" t="inlineStr"/>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Gothorita</t>
+          <t>Excadrill</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>37-39</t>
+          <t>35-37</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>16.67%</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Strange House</t>
+          <t>Reversal Mountain</t>
         </is>
       </c>
       <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Duosion</t>
+          <t>Lopunny</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>37-39</t>
+          <t>35-37</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>16.67%</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Undella Bay</t>
+          <t>Reversal Mountain</t>
         </is>
       </c>
       <c r="C113" t="inlineStr"/>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Barboach</t>
+          <t>Skorupi</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>39-40</t>
+          <t>35-37</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>16.67%</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Undella Bay</t>
+          <t>Reversal Mountain</t>
         </is>
       </c>
       <c r="C114" t="inlineStr"/>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Poliwag</t>
+          <t>Numel</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>39-40</t>
+          <t>35-37</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>16.67%</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Undella Bay</t>
+          <t>Strange House</t>
         </is>
       </c>
       <c r="C115" t="inlineStr"/>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Buizel</t>
+          <t>Litwick</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>39-40</t>
+          <t>37-39</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>11.120000000000005%</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Undella Bay</t>
+          <t>Strange House</t>
         </is>
       </c>
       <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Lumineon</t>
+          <t>Raticate</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>39-40</t>
+          <t>37-39</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>11.11%</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Undella Bay</t>
+          <t>Strange House</t>
         </is>
       </c>
       <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Corphish</t>
+          <t>Golbat</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>39-40</t>
+          <t>37-39</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>11.11%</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Undella Bay</t>
+          <t>Strange House</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Frillish</t>
+          <t>Banette</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>39-40</t>
+          <t>37-39</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>11.11%</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Undella Bay</t>
+          <t>Strange House</t>
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Kingler</t>
+          <t>Gothita</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>39-40</t>
+          <t>37-39</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>11.11%</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Undella Bay</t>
+          <t>Strange House</t>
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Marill</t>
+          <t>Solosis</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>39-40</t>
+          <t>37-39</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>11.11%</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Route 13</t>
+          <t>Strange House</t>
         </is>
       </c>
       <c r="C121" t="inlineStr"/>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Tangela</t>
+          <t>Gothorita</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>40-42</t>
+          <t>37-39</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>11.11%</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Route 13</t>
+          <t>Strange House</t>
         </is>
       </c>
       <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Drifblim</t>
+          <t>Duosion</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>40-42</t>
+          <t>37-39</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>11.11%</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Route 13</t>
+          <t>Strange House</t>
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Pelipper</t>
+          <t>Shuppet</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>40-42</t>
+          <t>37-39</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>11.11%</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Route 13</t>
+          <t>Undella Bay</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Absol</t>
+          <t>Barboach</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>40-42</t>
+          <t>39-40</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>11.120000000000005%</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Route 13</t>
+          <t>Undella Bay</t>
         </is>
       </c>
       <c r="C125" t="inlineStr"/>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Floatzel</t>
+          <t>Poliwag</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>40-42</t>
+          <t>39-40</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>11.11%</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Route 14</t>
+          <t>Undella Bay</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Altaria</t>
+          <t>Buizel</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>42-44</t>
+          <t>39-40</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>11.11%</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Route 14</t>
+          <t>Undella Bay</t>
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Absol</t>
+          <t>Lumineon</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>42-44</t>
+          <t>39-40</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>11.11%</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Route 14</t>
+          <t>Undella Bay</t>
         </is>
       </c>
       <c r="C128" t="inlineStr"/>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Mienfoo</t>
+          <t>Corphish</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>42-44</t>
+          <t>39-40</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>11.11%</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Route 14</t>
+          <t>Undella Bay</t>
         </is>
       </c>
       <c r="C129" t="inlineStr"/>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Golduck</t>
+          <t>Frillish</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>42-44</t>
+          <t>39-40</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>11.11%</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Route 14</t>
+          <t>Undella Bay</t>
         </is>
       </c>
       <c r="C130" t="inlineStr"/>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Swablu</t>
+          <t>Kingler</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>42-44</t>
+          <t>39-40</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>11.11%</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Abundant Shrine</t>
+          <t>Undella Bay</t>
         </is>
       </c>
       <c r="C131" t="inlineStr"/>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Vulpix</t>
+          <t>Marill</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>44-45</t>
+          <t>39-40</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>11.11%</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Abundant Shrine</t>
+          <t>Undella Bay</t>
         </is>
       </c>
       <c r="C132" t="inlineStr"/>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Bronzong</t>
+          <t>Wailmer</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>44-45</t>
+          <t>39-40</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>11.11%</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Abundant Shrine</t>
+          <t>Route 13</t>
         </is>
       </c>
       <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Swablu</t>
+          <t>Tangela</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>44-45</t>
+          <t>40-42</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>16.64999999999999%</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Abundant Shrine</t>
+          <t>Route 13</t>
         </is>
       </c>
       <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Chimecho</t>
+          <t>Drifblim</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>44-45</t>
+          <t>40-42</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>16.67%</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Abundant Shrine</t>
+          <t>Route 13</t>
         </is>
       </c>
       <c r="C135" t="inlineStr"/>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Gothitelle</t>
+          <t>Pelipper</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>44-45</t>
+          <t>40-42</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>16.67%</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Village Bridge</t>
+          <t>Route 13</t>
         </is>
       </c>
       <c r="C136" t="inlineStr"/>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Bibarel</t>
+          <t>Absol</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>45-47</t>
+          <t>40-42</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>16.67%</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Village Bridge</t>
+          <t>Route 13</t>
         </is>
       </c>
       <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Zebstrika</t>
+          <t>Floatzel</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>45-47</t>
+          <t>40-42</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>16.67%</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Village Bridge</t>
+          <t>Route 13</t>
         </is>
       </c>
       <c r="C138" t="inlineStr"/>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Pelipper</t>
+          <t>Drifloon</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>45-47</t>
+          <t>40-42</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>16.67%</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Village Bridge</t>
+          <t>Route 14</t>
         </is>
       </c>
       <c r="C139" t="inlineStr"/>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Dunsparce</t>
+          <t>Altaria</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>45-47</t>
+          <t>42-44</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>16.64999999999999%</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Village Bridge</t>
+          <t>Route 14</t>
         </is>
       </c>
       <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Loudred</t>
+          <t>Absol</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>45-47</t>
+          <t>42-44</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>16.67%</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Route 12</t>
+          <t>Route 14</t>
         </is>
       </c>
       <c r="C141" t="inlineStr"/>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Sewaddle</t>
+          <t>Mienfoo</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>47-49</t>
+          <t>42-44</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>16.67%</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Route 12</t>
+          <t>Route 14</t>
         </is>
       </c>
       <c r="C142" t="inlineStr"/>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Tranquill</t>
+          <t>Golduck</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>47-49</t>
+          <t>42-44</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>16.67%</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Route 12</t>
+          <t>Route 14</t>
         </is>
       </c>
       <c r="C143" t="inlineStr"/>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Roselia</t>
+          <t>Swablu</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>47-49</t>
+          <t>42-44</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>16.67%</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Route 12</t>
+          <t>Route 14</t>
         </is>
       </c>
       <c r="C144" t="inlineStr"/>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Combee</t>
+          <t>Tropius</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>47-49</t>
+          <t>42-44</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>16.67%</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Route 12</t>
+          <t>Abundant Shrine</t>
         </is>
       </c>
       <c r="C145" t="inlineStr"/>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Pinsir</t>
+          <t>Vulpix</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>47-49</t>
+          <t>44-45</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -4196,22 +4196,22 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Route 9</t>
+          <t>Abundant Shrine</t>
         </is>
       </c>
       <c r="C146" t="inlineStr"/>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Garbodor</t>
+          <t>Bronzong</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>49-51</t>
+          <t>44-45</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -4222,22 +4222,22 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Route 9</t>
+          <t>Abundant Shrine</t>
         </is>
       </c>
       <c r="C147" t="inlineStr"/>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Liepard</t>
+          <t>Swablu</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>49-51</t>
+          <t>44-45</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -4248,22 +4248,22 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Route 9</t>
+          <t>Abundant Shrine</t>
         </is>
       </c>
       <c r="C148" t="inlineStr"/>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Muk</t>
+          <t>Chimecho</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>49-51</t>
+          <t>44-45</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -4274,22 +4274,22 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Route 9</t>
+          <t>Abundant Shrine</t>
         </is>
       </c>
       <c r="C149" t="inlineStr"/>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Minccino</t>
+          <t>Gothitelle</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>49-51</t>
+          <t>44-45</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -4300,22 +4300,22 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Route 9</t>
+          <t>Village Bridge</t>
         </is>
       </c>
       <c r="C150" t="inlineStr"/>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Duosion</t>
+          <t>Bibarel</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>49-51</t>
+          <t>45-47</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -4326,22 +4326,22 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Route 10</t>
+          <t>Village Bridge</t>
         </is>
       </c>
       <c r="C151" t="inlineStr"/>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Bouffalant</t>
+          <t>Zebstrika</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>51-52</t>
+          <t>45-47</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -4352,22 +4352,22 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Route 10</t>
+          <t>Village Bridge</t>
         </is>
       </c>
       <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Braviary</t>
+          <t>Pelipper</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>51-52</t>
+          <t>45-47</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -4378,22 +4378,22 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Route 10</t>
+          <t>Village Bridge</t>
         </is>
       </c>
       <c r="C153" t="inlineStr"/>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Mandibuzz</t>
+          <t>Dunsparce</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>51-52</t>
+          <t>45-47</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -4404,22 +4404,22 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Route 10</t>
+          <t>Village Bridge</t>
         </is>
       </c>
       <c r="C154" t="inlineStr"/>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Amoonguss</t>
+          <t>Loudred</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>51-52</t>
+          <t>45-47</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -4430,22 +4430,22 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Route 10</t>
+          <t>Route 12</t>
         </is>
       </c>
       <c r="C155" t="inlineStr"/>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Eelektrik</t>
+          <t>Sewaddle</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>51-52</t>
+          <t>47-49</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -4456,464 +4456,464 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Driftveil Drawbridge</t>
+          <t>Route 12</t>
         </is>
       </c>
       <c r="C156" t="inlineStr"/>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Remoraid</t>
+          <t>Tranquill</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>52-54</t>
+          <t>47-49</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>14.259999999999998%</t>
+          <t>20.0%</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Driftveil Drawbridge</t>
+          <t>Route 12</t>
         </is>
       </c>
       <c r="C157" t="inlineStr"/>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Carvanha</t>
+          <t>Roselia</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>52-54</t>
+          <t>47-49</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>14.29%</t>
+          <t>20.0%</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Driftveil Drawbridge</t>
+          <t>Route 12</t>
         </is>
       </c>
       <c r="C158" t="inlineStr"/>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Chinchou</t>
+          <t>Combee</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>52-54</t>
+          <t>47-49</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>14.29%</t>
+          <t>20.0%</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Driftveil Drawbridge</t>
+          <t>Route 12</t>
         </is>
       </c>
       <c r="C159" t="inlineStr"/>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Finneon</t>
+          <t>Pinsir</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>52-54</t>
+          <t>47-49</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>14.29%</t>
+          <t>20.0%</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Driftveil Drawbridge</t>
+          <t>Route 9</t>
         </is>
       </c>
       <c r="C160" t="inlineStr"/>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Goldeen</t>
+          <t>Garbodor</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>52-54</t>
+          <t>49-51</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>14.29%</t>
+          <t>20.0%</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Driftveil Drawbridge</t>
+          <t>Route 9</t>
         </is>
       </c>
       <c r="C161" t="inlineStr"/>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Luvdisc</t>
+          <t>Liepard</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>52-54</t>
+          <t>49-51</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>14.29%</t>
+          <t>20.0%</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Driftveil Drawbridge</t>
+          <t>Route 9</t>
         </is>
       </c>
       <c r="C162" t="inlineStr"/>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Shellder</t>
+          <t>Muk</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>52-54</t>
+          <t>49-51</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>14.29%</t>
+          <t>20.0%</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Seaside Cave</t>
+          <t>Route 9</t>
         </is>
       </c>
       <c r="C163" t="inlineStr"/>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Boldore</t>
+          <t>Minccino</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>54-56</t>
+          <t>49-51</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Seaside Cave</t>
+          <t>Route 9</t>
         </is>
       </c>
       <c r="C164" t="inlineStr"/>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Feebas</t>
+          <t>Duosion</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>54-56</t>
+          <t>49-51</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Seaside Cave</t>
+          <t>Route 10</t>
         </is>
       </c>
       <c r="C165" t="inlineStr"/>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Alomomola</t>
+          <t>Bouffalant</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>54-56</t>
+          <t>51-52</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>16.64999999999999%</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Seaside Cave</t>
+          <t>Route 10</t>
         </is>
       </c>
       <c r="C166" t="inlineStr"/>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Woobat</t>
+          <t>Braviary</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>54-56</t>
+          <t>51-52</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>16.67%</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Route 21</t>
+          <t>Route 10</t>
         </is>
       </c>
       <c r="C167" t="inlineStr"/>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Mantyke</t>
+          <t>Mandibuzz</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>56-58</t>
+          <t>51-52</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>16.67%</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Route 21</t>
+          <t>Route 10</t>
         </is>
       </c>
       <c r="C168" t="inlineStr"/>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Luvdisc</t>
+          <t>Amoonguss</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>56-58</t>
+          <t>51-52</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>16.67%</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Route 21</t>
+          <t>Route 10</t>
         </is>
       </c>
       <c r="C169" t="inlineStr"/>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Corsola</t>
+          <t>Eelektrik</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>56-58</t>
+          <t>51-52</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>16.67%</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Route 21</t>
+          <t>Route 10</t>
         </is>
       </c>
       <c r="C170" t="inlineStr"/>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Wingull</t>
+          <t>Vullaby</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>56-58</t>
+          <t>51-52</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>16.67%</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Route 21</t>
+          <t>Driftveil Drawbridge</t>
         </is>
       </c>
       <c r="C171" t="inlineStr"/>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Pelipper</t>
+          <t>Remoraid</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>56-58</t>
+          <t>52-54</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>14.259999999999998%</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Humilau Sea</t>
+          <t>Driftveil Drawbridge</t>
         </is>
       </c>
       <c r="C172" t="inlineStr"/>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Feebas</t>
+          <t>Carvanha</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>58-59</t>
+          <t>52-54</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>14.259999999999998%</t>
+          <t>14.29%</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Humilau Sea</t>
+          <t>Driftveil Drawbridge</t>
         </is>
       </c>
       <c r="C173" t="inlineStr"/>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Finneon</t>
+          <t>Chinchou</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>58-59</t>
+          <t>52-54</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -4924,22 +4924,22 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Humilau Sea</t>
+          <t>Driftveil Drawbridge</t>
         </is>
       </c>
       <c r="C174" t="inlineStr"/>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Qwilfish</t>
+          <t>Finneon</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>58-59</t>
+          <t>52-54</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -4950,22 +4950,22 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Humilau Sea</t>
+          <t>Driftveil Drawbridge</t>
         </is>
       </c>
       <c r="C175" t="inlineStr"/>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Stunfisk</t>
+          <t>Goldeen</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>58-59</t>
+          <t>52-54</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -4976,22 +4976,22 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Humilau Sea</t>
+          <t>Driftveil Drawbridge</t>
         </is>
       </c>
       <c r="C176" t="inlineStr"/>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Palpitoad</t>
+          <t>Luvdisc</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>58-59</t>
+          <t>52-54</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -5002,22 +5002,22 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Humilau Sea</t>
+          <t>Driftveil Drawbridge</t>
         </is>
       </c>
       <c r="C177" t="inlineStr"/>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Poliwhirl</t>
+          <t>Shellder</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>58-59</t>
+          <t>52-54</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -5028,345 +5028,349 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Humilau Sea</t>
+          <t>Seaside Cave</t>
         </is>
       </c>
       <c r="C178" t="inlineStr"/>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Politoed</t>
+          <t>Boldore</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>58-59</t>
+          <t>54-56</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>14.29%</t>
+          <t>20.0%</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Route 23</t>
+          <t>Seaside Cave</t>
         </is>
       </c>
       <c r="C179" t="inlineStr"/>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Sneasel</t>
+          <t>Feebas</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>59-61</t>
+          <t>54-56</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>16.64999999999999%</t>
+          <t>20.0%</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Route 23</t>
+          <t>Seaside Cave</t>
         </is>
       </c>
       <c r="C180" t="inlineStr"/>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Amoonguss</t>
+          <t>Alomomola</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>59-61</t>
+          <t>54-56</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>16.67%</t>
+          <t>20.0%</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Route 23</t>
+          <t>Seaside Cave</t>
         </is>
       </c>
       <c r="C181" t="inlineStr"/>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Bouffalant</t>
+          <t>Woobat</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>59-61</t>
+          <t>54-56</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>16.67%</t>
+          <t>20.0%</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Route 23</t>
+          <t>Seaside Cave</t>
         </is>
       </c>
       <c r="C182" t="inlineStr"/>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Roserade</t>
+          <t>Shuckle</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>59-61</t>
+          <t>54-56</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>16.67%</t>
+          <t>20.0%</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Route 23</t>
+          <t>Route 21</t>
         </is>
       </c>
       <c r="C183" t="inlineStr"/>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Gurdurr</t>
+          <t>Mantyke</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>59-61</t>
+          <t>56-58</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>16.67%</t>
+          <t>20.0%</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Route 23</t>
+          <t>Route 21</t>
         </is>
       </c>
       <c r="C184" t="inlineStr"/>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Serperior</t>
+          <t>Luvdisc</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>59-61</t>
+          <t>56-58</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>16.67%</t>
+          <t>20.0%</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Victory Road</t>
+          <t>Route 21</t>
         </is>
       </c>
       <c r="C185" t="inlineStr"/>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Durant</t>
+          <t>Corsola</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>61-63</t>
+          <t>56-58</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Victory Road</t>
+          <t>Route 21</t>
         </is>
       </c>
       <c r="C186" t="inlineStr"/>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Heatmor</t>
+          <t>Wingull</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>61-63</t>
+          <t>56-58</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Victory Road</t>
+          <t>Route 21</t>
         </is>
       </c>
       <c r="C187" t="inlineStr"/>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Deino</t>
+          <t>Pelipper</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>61-63</t>
+          <t>56-58</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Victory Road</t>
+          <t>Humilau Sea</t>
         </is>
       </c>
       <c r="C188" t="inlineStr"/>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Druddigon</t>
+          <t>Feebas</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>61-63</t>
+          <t>58-59</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>14.259999999999998%</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Pokemon League</t>
+          <t>Humilau Sea</t>
         </is>
       </c>
       <c r="C189" t="inlineStr"/>
-      <c r="D189" t="inlineStr"/>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Finneon</t>
+        </is>
+      </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>63-65</t>
+          <t>58-59</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>14.29%</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Route 8</t>
+          <t>Humilau Sea</t>
         </is>
       </c>
       <c r="C190" t="inlineStr"/>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Palpitoad</t>
+          <t>Qwilfish</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>65-66</t>
+          <t>58-59</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>14.29%</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Route 8</t>
+          <t>Humilau Sea</t>
         </is>
       </c>
       <c r="C191" t="inlineStr"/>
@@ -5377,204 +5381,204 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>65-66</t>
+          <t>58-59</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>14.29%</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Route 8</t>
+          <t>Humilau Sea</t>
         </is>
       </c>
       <c r="C192" t="inlineStr"/>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Shellder</t>
+          <t>Palpitoad</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>65-66</t>
+          <t>58-59</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>14.29%</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Route 8</t>
+          <t>Humilau Sea</t>
         </is>
       </c>
       <c r="C193" t="inlineStr"/>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Croagunk</t>
+          <t>Poliwhirl</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>65-66</t>
+          <t>58-59</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>14.29%</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Dragonspiral Tower</t>
+          <t>Humilau Sea</t>
         </is>
       </c>
       <c r="C194" t="inlineStr"/>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Golett</t>
+          <t>Politoed</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>66-68</t>
+          <t>58-59</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>14.29%</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Dragonspiral Tower</t>
+          <t>Route 23</t>
         </is>
       </c>
       <c r="C195" t="inlineStr"/>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Druddigon</t>
+          <t>Sneasel</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>66-68</t>
+          <t>59-61</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>16.64999999999999%</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Dragonspiral Tower</t>
+          <t>Route 23</t>
         </is>
       </c>
       <c r="C196" t="inlineStr"/>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Mienfoo</t>
+          <t>Amoonguss</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>66-68</t>
+          <t>59-61</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>16.67%</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Dragonspiral Tower</t>
+          <t>Route 23</t>
         </is>
       </c>
       <c r="C197" t="inlineStr"/>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Golbat</t>
+          <t>Bouffalant</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>66-68</t>
+          <t>59-61</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>16.67%</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Twist Mountain</t>
+          <t>Route 23</t>
         </is>
       </c>
       <c r="C198" t="inlineStr"/>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Boldore</t>
+          <t>Roserade</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>68-70</t>
+          <t>59-61</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>16.67%</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Twist Mountain</t>
+          <t>Route 23</t>
         </is>
       </c>
       <c r="C199" t="inlineStr"/>
@@ -5585,59 +5589,59 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>68-70</t>
+          <t>59-61</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>16.67%</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Twist Mountain</t>
+          <t>Route 23</t>
         </is>
       </c>
       <c r="C200" t="inlineStr"/>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Cryogonal</t>
+          <t>Serperior</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>68-70</t>
+          <t>59-61</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>16.67%</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Twist Mountain</t>
+          <t>Victory Road</t>
         </is>
       </c>
       <c r="C201" t="inlineStr"/>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Woobat</t>
+          <t>Durant</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>68-70</t>
+          <t>61-63</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -5648,334 +5652,330 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Giant Chasm</t>
+          <t>Victory Road</t>
         </is>
       </c>
       <c r="C202" t="inlineStr"/>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Delibird</t>
+          <t>Heatmor</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>70-71</t>
+          <t>61-63</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>16.64999999999999%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Giant Chasm</t>
+          <t>Victory Road</t>
         </is>
       </c>
       <c r="C203" t="inlineStr"/>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Swinub</t>
+          <t>Deino</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>70-71</t>
+          <t>61-63</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>16.67%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Giant Chasm</t>
+          <t>Victory Road</t>
         </is>
       </c>
       <c r="C204" t="inlineStr"/>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Piloswine</t>
+          <t>Druddigon</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>70-71</t>
+          <t>61-63</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>16.67%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Giant Chasm</t>
+          <t>Pokemon League</t>
         </is>
       </c>
       <c r="C205" t="inlineStr"/>
-      <c r="D205" t="inlineStr">
-        <is>
-          <t>Ditto</t>
-        </is>
-      </c>
+      <c r="D205" t="inlineStr"/>
       <c r="E205" t="inlineStr">
         <is>
-          <t>70-71</t>
+          <t>63-65</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>16.67%</t>
+          <t>0%</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Giant Chasm</t>
+          <t>Route 8</t>
         </is>
       </c>
       <c r="C206" t="inlineStr"/>
       <c r="D206" t="inlineStr">
         <is>
-          <t>Clefairy</t>
+          <t>Palpitoad</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>70-71</t>
+          <t>65-66</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>16.67%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Giant Chasm</t>
+          <t>Route 8</t>
         </is>
       </c>
       <c r="C207" t="inlineStr"/>
       <c r="D207" t="inlineStr">
         <is>
-          <t>Metang</t>
+          <t>Stunfisk</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>70-71</t>
+          <t>65-66</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>16.67%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Underground Ruins</t>
+          <t>Route 8</t>
         </is>
       </c>
       <c r="C208" t="inlineStr"/>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Boldore</t>
+          <t>Shellder</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>71-73</t>
+          <t>65-66</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>16.64999999999999%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Underground Ruins</t>
+          <t>Route 8</t>
         </is>
       </c>
       <c r="C209" t="inlineStr"/>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Nosepass</t>
+          <t>Croagunk</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>71-73</t>
+          <t>65-66</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>16.67%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Underground Ruins</t>
+          <t>Dragonspiral Tower</t>
         </is>
       </c>
       <c r="C210" t="inlineStr"/>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Lairon</t>
+          <t>Golett</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>71-73</t>
+          <t>66-68</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>16.67%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Underground Ruins</t>
+          <t>Dragonspiral Tower</t>
         </is>
       </c>
       <c r="C211" t="inlineStr"/>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Woobat</t>
+          <t>Druddigon</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>71-73</t>
+          <t>66-68</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>16.67%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Underground Ruins</t>
+          <t>Dragonspiral Tower</t>
         </is>
       </c>
       <c r="C212" t="inlineStr"/>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Durant</t>
+          <t>Mienfoo</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>71-73</t>
+          <t>66-68</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>16.67%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Underground Ruins</t>
+          <t>Dragonspiral Tower</t>
         </is>
       </c>
       <c r="C213" t="inlineStr"/>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Onix</t>
+          <t>Golbat</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>71-73</t>
+          <t>66-68</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>16.67%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Route 15</t>
+          <t>Twist Mountain</t>
         </is>
       </c>
       <c r="C214" t="inlineStr"/>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Gligar</t>
+          <t>Boldore</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>73-75</t>
+          <t>68-70</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -5986,22 +5986,22 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Route 15</t>
+          <t>Twist Mountain</t>
         </is>
       </c>
       <c r="C215" t="inlineStr"/>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Pupitar</t>
+          <t>Gurdurr</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>73-75</t>
+          <t>68-70</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
@@ -6012,22 +6012,22 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Route 15</t>
+          <t>Twist Mountain</t>
         </is>
       </c>
       <c r="C216" t="inlineStr"/>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Scraggy</t>
+          <t>Cryogonal</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>73-75</t>
+          <t>68-70</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
@@ -6038,22 +6038,22 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Route 15</t>
+          <t>Twist Mountain</t>
         </is>
       </c>
       <c r="C217" t="inlineStr"/>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Foongus</t>
+          <t>Woobat</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>73-75</t>
+          <t>68-70</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -6064,22 +6064,22 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Route 15</t>
+          <t>Twist Mountain</t>
         </is>
       </c>
       <c r="C218" t="inlineStr"/>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Koffing</t>
+          <t>Larvitar</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>73-75</t>
+          <t>68-70</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
@@ -6090,620 +6090,620 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Route 18</t>
+          <t>Giant Chasm</t>
         </is>
       </c>
       <c r="C219" t="inlineStr"/>
       <c r="D219" t="inlineStr">
         <is>
-          <t>Scraggy</t>
+          <t>Delibird</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>75-76</t>
+          <t>70-71</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Route 18</t>
+          <t>Giant Chasm</t>
         </is>
       </c>
       <c r="C220" t="inlineStr"/>
       <c r="D220" t="inlineStr">
         <is>
-          <t>Crustle</t>
+          <t>Swinub</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>75-76</t>
+          <t>70-71</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Route 18</t>
+          <t>Giant Chasm</t>
         </is>
       </c>
       <c r="C221" t="inlineStr"/>
       <c r="D221" t="inlineStr">
         <is>
-          <t>Carnivine</t>
+          <t>Piloswine</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>75-76</t>
+          <t>70-71</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Route 18</t>
+          <t>Giant Chasm</t>
         </is>
       </c>
       <c r="C222" t="inlineStr"/>
       <c r="D222" t="inlineStr">
         <is>
-          <t>Drifblim</t>
+          <t>Ditto</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>75-76</t>
+          <t>70-71</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Cave of Being</t>
+          <t>Giant Chasm</t>
         </is>
       </c>
       <c r="C223" t="inlineStr"/>
       <c r="D223" t="inlineStr">
         <is>
-          <t>Roggenrola</t>
+          <t>Clefairy</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>76-78</t>
+          <t>70-71</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Cave of Being</t>
+          <t>Giant Chasm</t>
         </is>
       </c>
       <c r="C224" t="inlineStr"/>
       <c r="D224" t="inlineStr">
         <is>
-          <t>Axew</t>
+          <t>Metang</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>76-78</t>
+          <t>70-71</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Nature Sanctuary</t>
+          <t>Giant Chasm</t>
         </is>
       </c>
       <c r="C225" t="inlineStr"/>
       <c r="D225" t="inlineStr">
         <is>
-          <t>Yanma</t>
+          <t>Lunatone</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>78-80</t>
+          <t>70-71</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Nature Sanctuary</t>
+          <t>Giant Chasm</t>
         </is>
       </c>
       <c r="C226" t="inlineStr"/>
       <c r="D226" t="inlineStr">
         <is>
-          <t>Zorua</t>
+          <t>Solrock</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>78-80</t>
+          <t>70-71</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Pinwheel Forest</t>
+          <t>Underground Ruins</t>
         </is>
       </c>
       <c r="C227" t="inlineStr"/>
       <c r="D227" t="inlineStr">
         <is>
-          <t>Snivy</t>
+          <t>Boldore</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>80-81</t>
+          <t>71-73</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>16.64999999999999%</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Pinwheel Forest</t>
+          <t>Underground Ruins</t>
         </is>
       </c>
       <c r="C228" t="inlineStr"/>
       <c r="D228" t="inlineStr">
         <is>
-          <t>Pansage</t>
+          <t>Nosepass</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>80-81</t>
+          <t>71-73</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>16.67%</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Nacrene City</t>
+          <t>Underground Ruins</t>
         </is>
       </c>
       <c r="C229" t="inlineStr"/>
       <c r="D229" t="inlineStr">
         <is>
-          <t>Tympole</t>
+          <t>Lairon</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>81-83</t>
+          <t>71-73</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>16.67%</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Nacrene City</t>
+          <t>Underground Ruins</t>
         </is>
       </c>
       <c r="C230" t="inlineStr"/>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Budew</t>
+          <t>Woobat</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>81-83</t>
+          <t>71-73</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>16.67%</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Moor of Icirrus</t>
+          <t>Underground Ruins</t>
         </is>
       </c>
       <c r="C231" t="inlineStr"/>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Shelmet</t>
+          <t>Durant</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>83-85</t>
+          <t>71-73</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>16.67%</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Moor of Icirrus</t>
+          <t>Underground Ruins</t>
         </is>
       </c>
       <c r="C232" t="inlineStr"/>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Ducklett</t>
+          <t>Onix</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>83-85</t>
+          <t>71-73</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>16.67%</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Icirrus City</t>
+          <t>Route 15</t>
         </is>
       </c>
       <c r="C233" t="inlineStr"/>
       <c r="D233" t="inlineStr">
         <is>
-          <t>Lapras</t>
+          <t>Gligar</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>85-86</t>
+          <t>73-75</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Icirrus City</t>
+          <t>Route 15</t>
         </is>
       </c>
       <c r="C234" t="inlineStr"/>
       <c r="D234" t="inlineStr">
         <is>
-          <t>Tirtouga</t>
+          <t>Pupitar</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>85-86</t>
+          <t>73-75</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Striaton City</t>
+          <t>Route 15</t>
         </is>
       </c>
       <c r="C235" t="inlineStr"/>
       <c r="D235" t="inlineStr">
         <is>
-          <t>Panpour</t>
+          <t>Scraggy</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>86-88</t>
+          <t>73-75</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Striaton City</t>
+          <t>Route 15</t>
         </is>
       </c>
       <c r="C236" t="inlineStr"/>
       <c r="D236" t="inlineStr">
         <is>
-          <t>Pansear</t>
+          <t>Foongus</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>86-88</t>
+          <t>73-75</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Dreamyard</t>
+          <t>Route 15</t>
         </is>
       </c>
       <c r="C237" t="inlineStr"/>
       <c r="D237" t="inlineStr">
         <is>
-          <t>Munna</t>
+          <t>Koffing</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>88-90</t>
+          <t>73-75</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Dreamyard</t>
+          <t>Route 18</t>
         </is>
       </c>
       <c r="C238" t="inlineStr"/>
       <c r="D238" t="inlineStr">
         <is>
-          <t>Rufflet</t>
+          <t>Scraggy</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>88-90</t>
+          <t>75-76</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Wellspring Cave</t>
+          <t>Route 18</t>
         </is>
       </c>
       <c r="C239" t="inlineStr"/>
       <c r="D239" t="inlineStr">
         <is>
-          <t>Grimer</t>
+          <t>Crustle</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>90-91</t>
+          <t>75-76</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Wellspring Cave</t>
+          <t>Route 18</t>
         </is>
       </c>
       <c r="C240" t="inlineStr"/>
       <c r="D240" t="inlineStr">
         <is>
-          <t>Bronzor</t>
+          <t>Carnivine</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>90-91</t>
+          <t>75-76</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>P2 Laboratory</t>
+          <t>Route 18</t>
         </is>
       </c>
       <c r="C241" t="inlineStr"/>
       <c r="D241" t="inlineStr">
         <is>
-          <t>Beldum</t>
+          <t>Drifblim</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>91-93</t>
+          <t>75-76</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>P2 Laboratory</t>
+          <t>Cave of Being</t>
         </is>
       </c>
       <c r="C242" t="inlineStr"/>
       <c r="D242" t="inlineStr">
         <is>
-          <t>Pawniard</t>
+          <t>Roggenrola</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>91-93</t>
+          <t>76-78</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
@@ -6714,22 +6714,22 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Route 1</t>
+          <t>Cave of Being</t>
         </is>
       </c>
       <c r="C243" t="inlineStr"/>
       <c r="D243" t="inlineStr">
         <is>
-          <t>Tepig</t>
+          <t>Axew</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>93-95</t>
+          <t>76-78</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
@@ -6740,22 +6740,22 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Route 1</t>
+          <t>Nature Sanctuary</t>
         </is>
       </c>
       <c r="C244" t="inlineStr"/>
       <c r="D244" t="inlineStr">
         <is>
-          <t>Oshawott</t>
+          <t>Yanma</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>93-95</t>
+          <t>78-80</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
@@ -6766,22 +6766,22 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Route 2</t>
+          <t>Nature Sanctuary</t>
         </is>
       </c>
       <c r="C245" t="inlineStr"/>
       <c r="D245" t="inlineStr">
         <is>
-          <t>Blitzle</t>
+          <t>Zorua</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>95-96</t>
+          <t>78-80</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
@@ -6792,22 +6792,22 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Route 2</t>
+          <t>Pinwheel Forest</t>
         </is>
       </c>
       <c r="C246" t="inlineStr"/>
       <c r="D246" t="inlineStr">
         <is>
-          <t>Spoink</t>
+          <t>Snivy</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>95-96</t>
+          <t>80-81</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
@@ -6818,22 +6818,22 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Route 3</t>
+          <t>Pinwheel Forest</t>
         </is>
       </c>
       <c r="C247" t="inlineStr"/>
       <c r="D247" t="inlineStr">
         <is>
-          <t>Throh</t>
+          <t>Pansage</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>96-98</t>
+          <t>80-81</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
@@ -6844,22 +6844,22 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Route 3</t>
+          <t>Nacrene City</t>
         </is>
       </c>
       <c r="C248" t="inlineStr"/>
       <c r="D248" t="inlineStr">
         <is>
-          <t>Sawk</t>
+          <t>Tympole</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>96-98</t>
+          <t>81-83</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
@@ -6870,22 +6870,22 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Nuvema Town</t>
+          <t>Nacrene City</t>
         </is>
       </c>
       <c r="C249" t="inlineStr"/>
       <c r="D249" t="inlineStr">
         <is>
-          <t>Cleffa</t>
+          <t>Budew</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>98-100</t>
+          <t>81-83</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
@@ -6896,22 +6896,22 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Nuvema Town</t>
+          <t>Moor of Icirrus</t>
         </is>
       </c>
       <c r="C250" t="inlineStr"/>
       <c r="D250" t="inlineStr">
         <is>
-          <t>Igglybuff</t>
+          <t>Shelmet</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>98-100</t>
+          <t>83-85</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
@@ -6922,337 +6922,857 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Moor of Icirrus Depths</t>
+          <t>Moor of Icirrus</t>
         </is>
       </c>
       <c r="C251" t="inlineStr"/>
       <c r="D251" t="inlineStr">
         <is>
-          <t>Cobalion</t>
+          <t>Ducklett</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>83-85</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Moor of Icirrus Depths</t>
+          <t>Icirrus City</t>
         </is>
       </c>
       <c r="C252" t="inlineStr"/>
       <c r="D252" t="inlineStr">
         <is>
-          <t>Terrakion</t>
+          <t>Lapras</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>85-86</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Moor of Icirrus Depths</t>
+          <t>Icirrus City</t>
         </is>
       </c>
       <c r="C253" t="inlineStr"/>
       <c r="D253" t="inlineStr">
         <is>
-          <t>Virizion</t>
+          <t>Tirtouga</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>85-86</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Moor of Icirrus Depths</t>
+          <t>Striaton City</t>
         </is>
       </c>
       <c r="C254" t="inlineStr"/>
       <c r="D254" t="inlineStr">
         <is>
-          <t>Keldeo</t>
+          <t>Panpour</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>86-88</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Liberty Garden</t>
+          <t>Striaton City</t>
         </is>
       </c>
       <c r="C255" t="inlineStr"/>
       <c r="D255" t="inlineStr">
         <is>
-          <t>Victini</t>
+          <t>Pansear</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>86-88</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>33.34%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Liberty Garden</t>
+          <t>Dreamyard</t>
         </is>
       </c>
       <c r="C256" t="inlineStr"/>
       <c r="D256" t="inlineStr">
         <is>
-          <t>Meloetta</t>
+          <t>Munna</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>88-90</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>33.33%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Liberty Garden</t>
+          <t>Dreamyard</t>
         </is>
       </c>
       <c r="C257" t="inlineStr"/>
       <c r="D257" t="inlineStr">
         <is>
-          <t>Genesect</t>
+          <t>Rufflet</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>88-90</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>33.33%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Abundant Shrine Depths</t>
+          <t>Wellspring Cave</t>
         </is>
       </c>
       <c r="C258" t="inlineStr"/>
       <c r="D258" t="inlineStr">
         <is>
-          <t>Landorus</t>
+          <t>Grimer</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>90-91</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>33.34%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Abundant Shrine Depths</t>
+          <t>Wellspring Cave</t>
         </is>
       </c>
       <c r="C259" t="inlineStr"/>
       <c r="D259" t="inlineStr">
         <is>
-          <t>Thundurus</t>
+          <t>Bronzor</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>90-91</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>33.33%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Abundant Shrine Depths</t>
+          <t>P2 Laboratory</t>
         </is>
       </c>
       <c r="C260" t="inlineStr"/>
       <c r="D260" t="inlineStr">
         <is>
-          <t>Tornadus</t>
+          <t>Beldum</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>91-93</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>33.33%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>N's Castle</t>
+          <t>P2 Laboratory</t>
         </is>
       </c>
       <c r="C261" t="inlineStr"/>
       <c r="D261" t="inlineStr">
         <is>
-          <t>Kyurem</t>
+          <t>Pawniard</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>91-93</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>33.34%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>N's Castle</t>
+          <t>Route 1</t>
         </is>
       </c>
       <c r="C262" t="inlineStr"/>
       <c r="D262" t="inlineStr">
         <is>
-          <t>Reshiram</t>
+          <t>Tepig</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>93-95</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>33.33%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>N's Castle</t>
+          <t>Route 1</t>
         </is>
       </c>
       <c r="C263" t="inlineStr"/>
       <c r="D263" t="inlineStr">
         <is>
+          <t>Oshawott</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>93-95</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="n">
+        <v>56</v>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Route 2</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr"/>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>Blitzle</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>95-96</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>33.34%</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="n">
+        <v>56</v>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Route 2</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr"/>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>Spoink</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>95-96</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>33.33%</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="n">
+        <v>56</v>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Route 2</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr"/>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>Lickitung</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>95-96</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>33.33%</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="n">
+        <v>57</v>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Route 3</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr"/>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>Throh</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>96-98</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="n">
+        <v>57</v>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Route 3</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr"/>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>Sawk</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>96-98</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="n">
+        <v>58</v>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Nuvema Town</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr"/>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>Cleffa</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>98-100</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="n">
+        <v>58</v>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Nuvema Town</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr"/>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>Igglybuff</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>98-100</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="n">
+        <v>59</v>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Moor of Icirrus Depths</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr"/>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>Cobalion</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="n">
+        <v>59</v>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Moor of Icirrus Depths</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr"/>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>Terrakion</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="n">
+        <v>59</v>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Moor of Icirrus Depths</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr"/>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>Virizion</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="n">
+        <v>59</v>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Moor of Icirrus Depths</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr"/>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>Keldeo</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="n">
+        <v>60</v>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Liberty Garden</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr"/>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>Victini</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>33.34%</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="n">
+        <v>60</v>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Liberty Garden</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr"/>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>Meloetta</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>33.33%</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="n">
+        <v>60</v>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Liberty Garden</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr"/>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>Genesect</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>33.33%</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="n">
+        <v>61</v>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Abundant Shrine Depths</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr"/>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>Landorus</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>33.34%</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="n">
+        <v>61</v>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Abundant Shrine Depths</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr"/>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>Thundurus</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>33.33%</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="n">
+        <v>61</v>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Abundant Shrine Depths</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr"/>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>Tornadus</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>33.33%</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="n">
+        <v>62</v>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>N's Castle</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr"/>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>Kyurem</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>33.34%</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="n">
+        <v>62</v>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>N's Castle</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr"/>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>Reshiram</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>33.33%</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="n">
+        <v>62</v>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>N's Castle</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr"/>
+      <c r="D283" t="inlineStr">
+        <is>
           <t>Zekrom</t>
         </is>
       </c>
-      <c r="E263" t="inlineStr">
+      <c r="E283" t="inlineStr">
         <is>
           <t>120</t>
         </is>
       </c>
-      <c r="F263" t="inlineStr">
+      <c r="F283" t="inlineStr">
         <is>
           <t>33.33%</t>
         </is>
@@ -8337,7 +8857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D127"/>
+  <dimension ref="A1:D107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9377,34 +9897,34 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Vullaby</t>
+          <t>Sandslash</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Dark / Flying</t>
+          <t>Ground</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sandslash</t>
+          <t>Scrafty</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Ground</t>
+          <t>Dark / Fighting</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -9421,12 +9941,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Scrafty</t>
+          <t>Vibrava</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Dark / Fighting</t>
+          <t>Ground / Dragon</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -9443,7 +9963,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Vibrava</t>
+          <t>Flygon</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -9465,12 +9985,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Flygon</t>
+          <t>Cofagrigus</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Ground / Dragon</t>
+          <t>Ghost</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -9487,12 +10007,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Cofagrigus</t>
+          <t>Carracosta</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Ghost</t>
+          <t>Water / Rock</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -9509,12 +10029,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Carracosta</t>
+          <t>Archeops</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Water / Rock</t>
+          <t>Rock / Flying</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -9531,56 +10051,56 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Archen</t>
+          <t>Klang</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Rock / Flying</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Archeops</t>
+          <t>Klinklang</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Rock / Flying</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Klang</t>
+          <t>Vespiquen</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Bug / Flying</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -9597,12 +10117,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Klinklang</t>
+          <t>Zoroark</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Dark</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -9619,12 +10139,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Vespiquen</t>
+          <t>Swanna</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Bug / Flying</t>
+          <t>Water / Flying</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -9641,12 +10161,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Zoroark</t>
+          <t>Escavalier</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Dark</t>
+          <t>Bug / Steel</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -9663,12 +10183,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Swanna</t>
+          <t>Accelgor</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Water / Flying</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -9685,12 +10205,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Escavalier</t>
+          <t>Sawsbuck</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Bug / Steel</t>
+          <t>Normal / Grass</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -9707,12 +10227,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Accelgor</t>
+          <t>Probopass</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Rock / Steel</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -9729,12 +10249,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Sawsbuck</t>
+          <t>Aggron</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Normal / Grass</t>
+          <t>Steel / Rock</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -9751,34 +10271,34 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Castform</t>
+          <t>Claydol</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Ground / Psychic</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Probopass</t>
+          <t>Volcarona</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Rock / Steel</t>
+          <t>Bug / Fire</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -9795,34 +10315,34 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Aron</t>
+          <t>Galvantula</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Steel / Rock</t>
+          <t>Bug / Electric</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Aggron</t>
+          <t>Ferrothorn</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Steel / Rock</t>
+          <t>Grass / Steel</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -9839,100 +10359,100 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Baltoy</t>
+          <t>Eelektross</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Ground / Psychic</t>
+          <t>Electric</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Claydol</t>
+          <t>Fraxure</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Ground / Psychic</t>
+          <t>Dragon</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Larvesta</t>
+          <t>Haxorus</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Bug / Fire</t>
+          <t>Dragon</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Volcarona</t>
+          <t>Beheeyem</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Bug / Fire</t>
+          <t>Psychic</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Galvantula</t>
+          <t>Lampent</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Bug / Electric</t>
+          <t>Ghost / Fire</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -9949,12 +10469,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Ferrothorn</t>
+          <t>Chandelure</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Grass / Steel</t>
+          <t>Ghost / Fire</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -9971,12 +10491,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Eelektross</t>
+          <t>Beartic</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Electric</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -9993,12 +10513,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Fraxure</t>
+          <t>Drapion</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Dragon</t>
+          <t>Poison / Dark</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -10015,12 +10535,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Haxorus</t>
+          <t>Grumpig</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Dragon</t>
+          <t>Psychic</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -10037,56 +10557,56 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Zangoose</t>
+          <t>Tangrowth</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Grass</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Seviper</t>
+          <t>Mienshao</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Poison</t>
+          <t>Fighting</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Beheeyem</t>
+          <t>Gliscor</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Psychic</t>
+          <t>Ground / Flying</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -10103,12 +10623,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Lampent</t>
+          <t>Bisharp</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Ghost / Fire</t>
+          <t>Dark / Steel</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -10125,12 +10645,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Chandelure</t>
+          <t>Seismitoad</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Ghost / Fire</t>
+          <t>Water / Ground</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -10147,12 +10667,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Beartic</t>
+          <t>Mantine</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Water / Flying</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -10169,78 +10689,78 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Skorupi</t>
+          <t>Octillery</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Poison / Bug</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Drapion</t>
+          <t>Starmie</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Poison / Dark</t>
+          <t>Water / Psychic</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Numel</t>
+          <t>Wailord</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Fire / Ground</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Grumpig</t>
+          <t>Sealeo</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Psychic</t>
+          <t>Ice / Water</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -10257,100 +10777,100 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Drifloon</t>
+          <t>Walrein</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Ghost / Flying</t>
+          <t>Ice / Water</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Shuppet</t>
+          <t>Ninetales</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Ghost</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Lunatone</t>
+          <t>Weavile</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Rock / Psychic</t>
+          <t>Dark / Ice</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Solrock</t>
+          <t>Vanillish</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Rock / Psychic</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Tangrowth</t>
+          <t>Vanilluxe</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Grass</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -10367,12 +10887,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Mienshao</t>
+          <t>Mamoswine</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Fighting</t>
+          <t>Ice / Ground</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -10389,12 +10909,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Gliscor</t>
+          <t>Metagross</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Ground / Flying</t>
+          <t>Steel / Psychic</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -10411,12 +10931,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Bisharp</t>
+          <t>Dewgong</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Dark / Steel</t>
+          <t>Water / Ice</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -10433,12 +10953,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Seismitoad</t>
+          <t>Golurk</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Water / Ground</t>
+          <t>Ground / Ghost</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -10455,34 +10975,34 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Shuckle</t>
+          <t>Zweilous</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Bug / Rock</t>
+          <t>Dark / Dragon</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Mantine</t>
+          <t>Hydreigon</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Water / Flying</t>
+          <t>Dark / Dragon</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -10499,12 +11019,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Octillery</t>
+          <t>Vigoroth</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -10521,12 +11041,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Starmie</t>
+          <t>Slaking</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Water / Psychic</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -10543,56 +11063,56 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Wailmer</t>
+          <t>Crawdaunt</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Water / Dark</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Wailord</t>
+          <t>Jigglypuff</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Normal / Fairy</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Suggest: Route 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Sealeo</t>
+          <t>Wigglytuff</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Ice / Water</t>
+          <t>Normal / Fairy</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -10609,12 +11129,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Walrein</t>
+          <t>Lickilicky</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Ice / Water</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -10631,12 +11151,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Ninetales</t>
+          <t>Yanmega</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Bug / Flying</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -10653,12 +11173,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Weavile</t>
+          <t>Toxicroak</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Dark / Ice</t>
+          <t>Poison / Fighting</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -10675,12 +11195,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Vanillish</t>
+          <t>Tyranitar</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Rock / Dark</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -10689,446 +11209,6 @@
         </is>
       </c>
       <c r="D107" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Vanilluxe</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Ice</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Mamoswine</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>Ice / Ground</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Metagross</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Steel / Psychic</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Dewgong</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>Water / Ice</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Golurk</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Ground / Ghost</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Zweilous</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Dark / Dragon</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Hydreigon</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>Dark / Dragon</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Slakoth</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Suggest: Route 1</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Vigoroth</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Suggest: Route 1</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Slaking</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Suggest: Route 1</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>Crawdaunt</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>Water / Dark</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>Jigglypuff</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>Normal / Fairy</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>Wigglytuff</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>Normal / Fairy</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>Lickitung</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Suggest: Route 1</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>Lickilicky</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Suggest: Route 1</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>Yanmega</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>Bug / Flying</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>Tropius</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>Grass / Flying</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Suggest: Route 1</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>Toxicroak</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>Poison / Fighting</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>Larvitar</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>Rock / Ground</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Suggest: Route 1</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>Tyranitar</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Rock / Dark</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
